--- a/hall/resources/sample/MedalBuff.xlsx
+++ b/hall/resources/sample/MedalBuff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="MedalBuff" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>序号</t>
   </si>
@@ -98,12 +98,21 @@
     <t>加成效果</t>
   </si>
   <si>
+    <t>BUFF描述</t>
+  </si>
+  <si>
+    <t>#备注</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>Map&lt;int{_}int&gt;{|}</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -116,16 +125,31 @@
     <t>BuffId</t>
   </si>
   <si>
-    <t>12405_1000</t>
-  </si>
-  <si>
-    <t>12404_1000</t>
+    <t>BuffStr</t>
+  </si>
+  <si>
+    <t>12405_100</t>
+  </si>
+  <si>
+    <t>产出金币的所有房间收益：+(%s)/min</t>
+  </si>
+  <si>
+    <t>12404_100</t>
+  </si>
+  <si>
+    <t>[运营部]知名度上限：+(%s)</t>
   </si>
   <si>
     <t>12406_1000</t>
   </si>
   <si>
-    <t>12408_2000</t>
+    <t>[营销部]曝光度上限：+(%s)</t>
+  </si>
+  <si>
+    <t>12408_100</t>
+  </si>
+  <si>
+    <t>[观看广告]金币收益：+(%s)</t>
   </si>
 </sst>
 </file>
@@ -350,7 +374,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,13 +383,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.8"/>
+        <fgColor theme="6" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -688,7 +706,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
@@ -712,16 +730,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7">
@@ -730,85 +748,85 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -831,8 +849,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -840,7 +858,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1188,8 +1206,8 @@
     <col min="2" max="2" width="15.4333333333333" style="4" customWidth="1"/>
     <col min="3" max="3" width="13.875" style="4" customWidth="1"/>
     <col min="4" max="4" width="22.6416666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="14.5583333333333" style="4" customWidth="1"/>
-    <col min="6" max="6" width="8.875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="18.75" style="4" customWidth="1"/>
+    <col min="6" max="6" width="33.625" style="4" customWidth="1"/>
     <col min="7" max="7" width="17.3416666666667" style="4" customWidth="1"/>
     <col min="8" max="8" width="11.125" style="4" customWidth="1"/>
     <col min="9" max="9" width="18.675" style="4" customWidth="1"/>
@@ -1206,14 +1224,18 @@
       <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
       <c r="I1" s="7"/>
@@ -1221,18 +1243,20 @@
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A2" s="5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="7"/>
+        <v>7</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="7"/>
@@ -1241,18 +1265,20 @@
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="7"/>
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -1276,7 +1302,13 @@
         <v>5</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" customHeight="1" spans="1:10">
@@ -1290,10 +1322,14 @@
         <v>5</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="E6" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -1310,10 +1346,14 @@
         <v>8</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="E7" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -1330,7 +1370,13 @@
         <v>8</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>13</v>
+        <v>20</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9" s="3" customFormat="1" customHeight="1" spans="1:10">

--- a/hall/resources/sample/MedalBuff.xlsx
+++ b/hall/resources/sample/MedalBuff.xlsx
@@ -50,10 +50,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1. 精英勋章
-2. 大亨勋章
-3. 富翁勋章
-4. 神豪勋章</t>
+与道具表中的品质一致</t>
         </r>
       </text>
     </comment>
@@ -1296,7 +1293,7 @@
         <v>101</v>
       </c>
       <c r="B5" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="11">
         <v>5</v>
@@ -1316,7 +1313,7 @@
         <v>102</v>
       </c>
       <c r="B6" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="11">
         <v>5</v>
@@ -1340,7 +1337,7 @@
         <v>103</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="11">
         <v>8</v>
@@ -1364,7 +1361,7 @@
         <v>104</v>
       </c>
       <c r="B8" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="11">
         <v>8</v>

--- a/hall/resources/sample/MedalBuff.xlsx
+++ b/hall/resources/sample/MedalBuff.xlsx
@@ -1296,7 +1296,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>14</v>
@@ -1316,7 +1316,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>16</v>
@@ -1340,7 +1340,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="11">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>18</v>
@@ -1364,7 +1364,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="11">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>20</v>

--- a/hall/resources/sample/MedalBuff.xlsx
+++ b/hall/resources/sample/MedalBuff.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="MedalBuff" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -80,8 +87,40 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+读取条件表“condition.xlsx”中的ID</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="59">
   <si>
     <t>序号</t>
   </si>
@@ -147,6 +186,117 @@
   </si>
   <si>
     <t>[观看广告]金币收益：+(%s)</t>
+  </si>
+  <si>
+    <t>徽章ID</t>
+  </si>
+  <si>
+    <t>建筑ID</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>buildID</t>
+  </si>
+  <si>
+    <t>愤怒的小鸟</t>
+  </si>
+  <si>
+    <t>12405_150</t>
+  </si>
+  <si>
+    <t>12405_200</t>
+  </si>
+  <si>
+    <t>12405_250</t>
+  </si>
+  <si>
+    <t>12405_300</t>
+  </si>
+  <si>
+    <t>12405_350</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>12404_150</t>
+  </si>
+  <si>
+    <t>12404_200</t>
+  </si>
+  <si>
+    <t>12404_250</t>
+  </si>
+  <si>
+    <t>12404_300</t>
+  </si>
+  <si>
+    <t>12404_350</t>
+  </si>
+  <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>12406_100</t>
+  </si>
+  <si>
+    <t>12406_150</t>
+  </si>
+  <si>
+    <t>12406_200</t>
+  </si>
+  <si>
+    <t>12406_250</t>
+  </si>
+  <si>
+    <t>12406_300</t>
+  </si>
+  <si>
+    <t>12406_350</t>
+  </si>
+  <si>
+    <t>财神来了</t>
+  </si>
+  <si>
+    <t>12408_150</t>
+  </si>
+  <si>
+    <t>12408_200</t>
+  </si>
+  <si>
+    <t>12408_250</t>
+  </si>
+  <si>
+    <t>12408_300</t>
+  </si>
+  <si>
+    <t>12408_350</t>
+  </si>
+  <si>
+    <t>寒冰王座</t>
+  </si>
+  <si>
+    <t>绿巨人</t>
+  </si>
+  <si>
+    <t>篮球巨星</t>
+  </si>
+  <si>
+    <t>宙斯VS哈迪斯</t>
+  </si>
+  <si>
+    <t>狼月</t>
+  </si>
+  <si>
+    <t>麻将胡了</t>
+  </si>
+  <si>
+    <t>雷神</t>
+  </si>
+  <si>
+    <t>杰克船长</t>
   </si>
 </sst>
 </file>
@@ -874,9 +1024,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -884,6 +1031,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1496,46 +1646,46 @@
       <c r="J19" s="12"/>
     </row>
     <row r="20" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="17"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="16"/>
     </row>
     <row r="21" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="18"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="17"/>
     </row>
     <row r="22" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="18"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="17"/>
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A23" s="11"/>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
-      <c r="D23" s="15"/>
+      <c r="D23" s="18"/>
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A24" s="11"/>
@@ -1598,4 +1748,2039 @@
   <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L76"/>
+  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="11.3166666666667" style="4" customWidth="1"/>
+    <col min="2" max="3" width="15.4333333333333" style="4" customWidth="1"/>
+    <col min="4" max="5" width="13.875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="22.6416666666667" style="4" customWidth="1"/>
+    <col min="7" max="7" width="18.75" style="4" customWidth="1"/>
+    <col min="8" max="8" width="33.625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="17.3416666666667" style="4" customWidth="1"/>
+    <col min="10" max="10" width="11.125" style="4" customWidth="1"/>
+    <col min="11" max="11" width="18.675" style="4" customWidth="1"/>
+    <col min="12" max="12" width="43.75" style="4" customWidth="1"/>
+    <col min="13" max="13" width="15.625" style="4"/>
+    <col min="14" max="14" width="9.125" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="15.625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="8"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="8"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+    </row>
+    <row r="5" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A5" s="11">
+        <v>1001</v>
+      </c>
+      <c r="B5" s="11">
+        <v>1</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1101</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="11">
+        <v>5</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A6" s="11">
+        <v>1002</v>
+      </c>
+      <c r="B6" s="11">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11">
+        <v>1101</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="11">
+        <v>15</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="11"/>
+    </row>
+    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A7" s="11">
+        <v>1003</v>
+      </c>
+      <c r="B7" s="11">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11">
+        <v>1101</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="11">
+        <v>25</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="11"/>
+    </row>
+    <row r="8" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A8" s="11">
+        <v>1004</v>
+      </c>
+      <c r="B8" s="11">
+        <v>1</v>
+      </c>
+      <c r="C8" s="11">
+        <v>1101</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="11">
+        <v>35</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A9" s="11">
+        <v>1005</v>
+      </c>
+      <c r="B9" s="11">
+        <v>1</v>
+      </c>
+      <c r="C9" s="11">
+        <v>1101</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="11">
+        <v>45</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A10" s="11">
+        <v>1006</v>
+      </c>
+      <c r="B10" s="11">
+        <v>1</v>
+      </c>
+      <c r="C10" s="11">
+        <v>1101</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="11">
+        <v>50</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" s="12"/>
+    </row>
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A11" s="11">
+        <v>1101</v>
+      </c>
+      <c r="B11" s="11">
+        <v>2</v>
+      </c>
+      <c r="C11" s="11">
+        <v>1102</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="11">
+        <v>5</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A12" s="11">
+        <v>1102</v>
+      </c>
+      <c r="B12" s="11">
+        <v>2</v>
+      </c>
+      <c r="C12" s="11">
+        <v>1102</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="11">
+        <v>15</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A13" s="11">
+        <v>1103</v>
+      </c>
+      <c r="B13" s="11">
+        <v>2</v>
+      </c>
+      <c r="C13" s="11">
+        <v>1102</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="11">
+        <v>25</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" s="12"/>
+    </row>
+    <row r="14" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A14" s="11">
+        <v>1104</v>
+      </c>
+      <c r="B14" s="11">
+        <v>2</v>
+      </c>
+      <c r="C14" s="11">
+        <v>1102</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="11">
+        <v>35</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A15" s="11">
+        <v>1105</v>
+      </c>
+      <c r="B15" s="11">
+        <v>2</v>
+      </c>
+      <c r="C15" s="11">
+        <v>1102</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="11">
+        <v>45</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15" s="12"/>
+    </row>
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A16" s="11">
+        <v>1106</v>
+      </c>
+      <c r="B16" s="11">
+        <v>2</v>
+      </c>
+      <c r="C16" s="11">
+        <v>1102</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="11">
+        <v>50</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16" s="12"/>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A17" s="13">
+        <v>1201</v>
+      </c>
+      <c r="B17" s="13">
+        <v>3</v>
+      </c>
+      <c r="C17" s="13">
+        <v>1103</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="11">
+        <v>5</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+    </row>
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A18" s="13">
+        <v>1202</v>
+      </c>
+      <c r="B18" s="13">
+        <v>3</v>
+      </c>
+      <c r="C18" s="13">
+        <v>1103</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="11">
+        <v>15</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="12"/>
+    </row>
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A19" s="13">
+        <v>1203</v>
+      </c>
+      <c r="B19" s="13">
+        <v>3</v>
+      </c>
+      <c r="C19" s="13">
+        <v>1103</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="11">
+        <v>25</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="12"/>
+    </row>
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A20" s="13">
+        <v>1204</v>
+      </c>
+      <c r="B20" s="13">
+        <v>3</v>
+      </c>
+      <c r="C20" s="13">
+        <v>1103</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="11">
+        <v>35</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="16"/>
+    </row>
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A21" s="13">
+        <v>1205</v>
+      </c>
+      <c r="B21" s="13">
+        <v>3</v>
+      </c>
+      <c r="C21" s="13">
+        <v>1103</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="11">
+        <v>45</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G21" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="17"/>
+    </row>
+    <row r="22" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A22" s="13">
+        <v>1206</v>
+      </c>
+      <c r="B22" s="13">
+        <v>3</v>
+      </c>
+      <c r="C22" s="13">
+        <v>1103</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="11">
+        <v>50</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="17"/>
+    </row>
+    <row r="23" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A23" s="11">
+        <v>1301</v>
+      </c>
+      <c r="B23" s="11">
+        <v>4</v>
+      </c>
+      <c r="C23" s="11">
+        <v>1104</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="11">
+        <v>5</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A24" s="11">
+        <v>1302</v>
+      </c>
+      <c r="B24" s="11">
+        <v>4</v>
+      </c>
+      <c r="C24" s="11">
+        <v>1104</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="11">
+        <v>15</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="12"/>
+    </row>
+    <row r="25" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="11">
+        <v>1303</v>
+      </c>
+      <c r="B25" s="11">
+        <v>4</v>
+      </c>
+      <c r="C25" s="11">
+        <v>1104</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="11">
+        <v>25</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A26" s="11">
+        <v>1304</v>
+      </c>
+      <c r="B26" s="11">
+        <v>4</v>
+      </c>
+      <c r="C26" s="11">
+        <v>1104</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="11">
+        <v>35</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A27" s="11">
+        <v>1305</v>
+      </c>
+      <c r="B27" s="11">
+        <v>4</v>
+      </c>
+      <c r="C27" s="11">
+        <v>1104</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="11">
+        <v>45</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G27" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="12"/>
+    </row>
+    <row r="28" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A28" s="11">
+        <v>1306</v>
+      </c>
+      <c r="B28" s="11">
+        <v>4</v>
+      </c>
+      <c r="C28" s="11">
+        <v>1104</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="11">
+        <v>50</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G28" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="12"/>
+    </row>
+    <row r="29" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A29" s="3">
+        <v>1401</v>
+      </c>
+      <c r="B29" s="3">
+        <v>5</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1105</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="11">
+        <v>5</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:12">
+      <c r="A30" s="3">
+        <v>1402</v>
+      </c>
+      <c r="B30" s="3">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1105</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="11">
+        <v>15</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:12">
+      <c r="A31" s="3">
+        <v>1403</v>
+      </c>
+      <c r="B31" s="3">
+        <v>5</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1105</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="11">
+        <v>25</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:12">
+      <c r="A32" s="3">
+        <v>1404</v>
+      </c>
+      <c r="B32" s="3">
+        <v>5</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1105</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="11">
+        <v>35</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G32" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:8">
+      <c r="A33" s="3">
+        <v>1405</v>
+      </c>
+      <c r="B33" s="3">
+        <v>5</v>
+      </c>
+      <c r="C33" s="3">
+        <v>1105</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="11">
+        <v>45</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:8">
+      <c r="A34" s="3">
+        <v>1406</v>
+      </c>
+      <c r="B34" s="3">
+        <v>5</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1105</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="11">
+        <v>50</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G34" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:8">
+      <c r="A35" s="4">
+        <v>1501</v>
+      </c>
+      <c r="B35" s="4">
+        <v>6</v>
+      </c>
+      <c r="C35" s="4">
+        <v>1106</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="11">
+        <v>5</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:8">
+      <c r="A36" s="4">
+        <v>1501</v>
+      </c>
+      <c r="B36" s="4">
+        <v>6</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1106</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="11">
+        <v>15</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:8">
+      <c r="A37" s="4">
+        <v>1501</v>
+      </c>
+      <c r="B37" s="4">
+        <v>6</v>
+      </c>
+      <c r="C37" s="4">
+        <v>1106</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="11">
+        <v>25</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G37" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:8">
+      <c r="A38" s="4">
+        <v>1501</v>
+      </c>
+      <c r="B38" s="4">
+        <v>6</v>
+      </c>
+      <c r="C38" s="4">
+        <v>1106</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E38" s="11">
+        <v>35</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:8">
+      <c r="A39" s="4">
+        <v>1501</v>
+      </c>
+      <c r="B39" s="4">
+        <v>6</v>
+      </c>
+      <c r="C39" s="4">
+        <v>1106</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="11">
+        <v>45</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G39" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:8">
+      <c r="A40" s="4">
+        <v>1501</v>
+      </c>
+      <c r="B40" s="4">
+        <v>6</v>
+      </c>
+      <c r="C40" s="4">
+        <v>1106</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="11">
+        <v>50</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G40" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:8">
+      <c r="A41" s="4">
+        <v>1601</v>
+      </c>
+      <c r="B41" s="4">
+        <v>7</v>
+      </c>
+      <c r="C41" s="4">
+        <v>1107</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="11">
+        <v>5</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G41" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:8">
+      <c r="A42" s="4">
+        <v>1602</v>
+      </c>
+      <c r="B42" s="4">
+        <v>7</v>
+      </c>
+      <c r="C42" s="4">
+        <v>1107</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E42" s="11">
+        <v>15</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G42" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:8">
+      <c r="A43" s="4">
+        <v>1603</v>
+      </c>
+      <c r="B43" s="4">
+        <v>7</v>
+      </c>
+      <c r="C43" s="4">
+        <v>1107</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" s="11">
+        <v>25</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G43" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:8">
+      <c r="A44" s="4">
+        <v>1604</v>
+      </c>
+      <c r="B44" s="4">
+        <v>7</v>
+      </c>
+      <c r="C44" s="4">
+        <v>1107</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="11">
+        <v>35</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G44" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:8">
+      <c r="A45" s="4">
+        <v>1605</v>
+      </c>
+      <c r="B45" s="4">
+        <v>7</v>
+      </c>
+      <c r="C45" s="4">
+        <v>1107</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="11">
+        <v>45</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G45" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:8">
+      <c r="A46" s="4">
+        <v>1606</v>
+      </c>
+      <c r="B46" s="4">
+        <v>7</v>
+      </c>
+      <c r="C46" s="4">
+        <v>1107</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="11">
+        <v>50</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G46" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:8">
+      <c r="A47" s="4">
+        <v>1701</v>
+      </c>
+      <c r="B47" s="4">
+        <v>8</v>
+      </c>
+      <c r="C47" s="4">
+        <v>1108</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" s="11">
+        <v>5</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:8">
+      <c r="A48" s="4">
+        <v>1702</v>
+      </c>
+      <c r="B48" s="4">
+        <v>8</v>
+      </c>
+      <c r="C48" s="4">
+        <v>1108</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E48" s="11">
+        <v>15</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G48" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:8">
+      <c r="A49" s="4">
+        <v>1703</v>
+      </c>
+      <c r="B49" s="4">
+        <v>8</v>
+      </c>
+      <c r="C49" s="4">
+        <v>1108</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E49" s="11">
+        <v>25</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G49" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:8">
+      <c r="A50" s="4">
+        <v>1704</v>
+      </c>
+      <c r="B50" s="4">
+        <v>8</v>
+      </c>
+      <c r="C50" s="4">
+        <v>1108</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" s="11">
+        <v>35</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G50" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:8">
+      <c r="A51" s="4">
+        <v>1705</v>
+      </c>
+      <c r="B51" s="4">
+        <v>8</v>
+      </c>
+      <c r="C51" s="4">
+        <v>1108</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E51" s="11">
+        <v>45</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G51" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:8">
+      <c r="A52" s="4">
+        <v>1706</v>
+      </c>
+      <c r="B52" s="4">
+        <v>8</v>
+      </c>
+      <c r="C52" s="4">
+        <v>1108</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E52" s="11">
+        <v>50</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G52" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:8">
+      <c r="A53" s="4">
+        <v>1801</v>
+      </c>
+      <c r="B53" s="4">
+        <v>9</v>
+      </c>
+      <c r="C53" s="4">
+        <v>1109</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E53" s="11">
+        <v>5</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:8">
+      <c r="A54" s="4">
+        <v>1802</v>
+      </c>
+      <c r="B54" s="4">
+        <v>9</v>
+      </c>
+      <c r="C54" s="4">
+        <v>1109</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E54" s="11">
+        <v>15</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G54" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:8">
+      <c r="A55" s="4">
+        <v>1803</v>
+      </c>
+      <c r="B55" s="4">
+        <v>9</v>
+      </c>
+      <c r="C55" s="4">
+        <v>1109</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" s="11">
+        <v>25</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:8">
+      <c r="A56" s="4">
+        <v>1804</v>
+      </c>
+      <c r="B56" s="4">
+        <v>9</v>
+      </c>
+      <c r="C56" s="4">
+        <v>1109</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E56" s="11">
+        <v>35</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G56" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:8">
+      <c r="A57" s="4">
+        <v>1805</v>
+      </c>
+      <c r="B57" s="4">
+        <v>9</v>
+      </c>
+      <c r="C57" s="4">
+        <v>1109</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E57" s="11">
+        <v>45</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G57" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:8">
+      <c r="A58" s="4">
+        <v>1806</v>
+      </c>
+      <c r="B58" s="4">
+        <v>9</v>
+      </c>
+      <c r="C58" s="4">
+        <v>1109</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E58" s="11">
+        <v>50</v>
+      </c>
+      <c r="F58" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G58" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:8">
+      <c r="A59" s="4">
+        <v>1901</v>
+      </c>
+      <c r="B59" s="4">
+        <v>10</v>
+      </c>
+      <c r="C59" s="4">
+        <v>1110</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E59" s="11">
+        <v>5</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:8">
+      <c r="A60" s="4">
+        <v>1902</v>
+      </c>
+      <c r="B60" s="4">
+        <v>10</v>
+      </c>
+      <c r="C60" s="4">
+        <v>1110</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E60" s="11">
+        <v>15</v>
+      </c>
+      <c r="F60" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G60" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:8">
+      <c r="A61" s="4">
+        <v>1903</v>
+      </c>
+      <c r="B61" s="4">
+        <v>10</v>
+      </c>
+      <c r="C61" s="4">
+        <v>1110</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E61" s="11">
+        <v>25</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G61" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:8">
+      <c r="A62" s="4">
+        <v>1904</v>
+      </c>
+      <c r="B62" s="4">
+        <v>10</v>
+      </c>
+      <c r="C62" s="4">
+        <v>1110</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E62" s="11">
+        <v>35</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G62" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="1:8">
+      <c r="A63" s="4">
+        <v>1905</v>
+      </c>
+      <c r="B63" s="4">
+        <v>10</v>
+      </c>
+      <c r="C63" s="4">
+        <v>1110</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E63" s="11">
+        <v>45</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G63" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="1:8">
+      <c r="A64" s="4">
+        <v>1906</v>
+      </c>
+      <c r="B64" s="4">
+        <v>10</v>
+      </c>
+      <c r="C64" s="4">
+        <v>1110</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E64" s="11">
+        <v>50</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G64" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:8">
+      <c r="A65" s="4">
+        <v>2001</v>
+      </c>
+      <c r="B65" s="4">
+        <v>11</v>
+      </c>
+      <c r="C65" s="4">
+        <v>1111</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E65" s="11">
+        <v>5</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="G65" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="1:8">
+      <c r="A66" s="4">
+        <v>2002</v>
+      </c>
+      <c r="B66" s="4">
+        <v>11</v>
+      </c>
+      <c r="C66" s="4">
+        <v>1111</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E66" s="11">
+        <v>15</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G66" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="1:8">
+      <c r="A67" s="4">
+        <v>2003</v>
+      </c>
+      <c r="B67" s="4">
+        <v>11</v>
+      </c>
+      <c r="C67" s="4">
+        <v>1111</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E67" s="11">
+        <v>25</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G67" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="1:8">
+      <c r="A68" s="4">
+        <v>2004</v>
+      </c>
+      <c r="B68" s="4">
+        <v>11</v>
+      </c>
+      <c r="C68" s="4">
+        <v>1111</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E68" s="11">
+        <v>35</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G68" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="1:8">
+      <c r="A69" s="4">
+        <v>2005</v>
+      </c>
+      <c r="B69" s="4">
+        <v>11</v>
+      </c>
+      <c r="C69" s="4">
+        <v>1111</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E69" s="11">
+        <v>45</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G69" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="1:8">
+      <c r="A70" s="4">
+        <v>2006</v>
+      </c>
+      <c r="B70" s="4">
+        <v>11</v>
+      </c>
+      <c r="C70" s="4">
+        <v>1111</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E70" s="11">
+        <v>50</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="1:8">
+      <c r="A71" s="4">
+        <v>2101</v>
+      </c>
+      <c r="B71" s="4">
+        <v>12</v>
+      </c>
+      <c r="C71" s="4">
+        <v>1112</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E71" s="11">
+        <v>5</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="1:8">
+      <c r="A72" s="4">
+        <v>2102</v>
+      </c>
+      <c r="B72" s="4">
+        <v>12</v>
+      </c>
+      <c r="C72" s="4">
+        <v>1112</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E72" s="11">
+        <v>15</v>
+      </c>
+      <c r="F72" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G72" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:8">
+      <c r="A73" s="4">
+        <v>2103</v>
+      </c>
+      <c r="B73" s="4">
+        <v>12</v>
+      </c>
+      <c r="C73" s="4">
+        <v>1112</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E73" s="11">
+        <v>25</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G73" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="1:8">
+      <c r="A74" s="4">
+        <v>2104</v>
+      </c>
+      <c r="B74" s="4">
+        <v>12</v>
+      </c>
+      <c r="C74" s="4">
+        <v>1112</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E74" s="11">
+        <v>35</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G74" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="1:8">
+      <c r="A75" s="4">
+        <v>2105</v>
+      </c>
+      <c r="B75" s="4">
+        <v>12</v>
+      </c>
+      <c r="C75" s="4">
+        <v>1112</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E75" s="11">
+        <v>45</v>
+      </c>
+      <c r="F75" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G75" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="1:8">
+      <c r="A76" s="4">
+        <v>2106</v>
+      </c>
+      <c r="B76" s="4">
+        <v>12</v>
+      </c>
+      <c r="C76" s="4">
+        <v>1112</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E76" s="11">
+        <v>50</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="G76" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/hall/resources/sample/MedalBuff.xlsx
+++ b/hall/resources/sample/MedalBuff.xlsx
@@ -12,9 +12,8 @@
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="MedalBuff" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
+    <sheet name="MedalBuff" sheetId="3" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,60 +38,6 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-与道具表中的品质一致</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-读取条件表“condition.xlsx”中的ID</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Administrator</author>
-  </authors>
-  <commentList>
     <comment ref="F1" authorId="0">
       <text>
         <r>
@@ -111,7 +56,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-读取条件表“condition.xlsx”中的ID</t>
+读取建筑表“BuildingAreaTable”中“typeValue”这个字段的属性</t>
         </r>
       </text>
     </comment>
@@ -120,12 +65,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="57">
   <si>
     <t>序号</t>
   </si>
   <si>
-    <t>勋章品质</t>
+    <t>徽章ID</t>
+  </si>
+  <si>
+    <t>建筑ID</t>
+  </si>
+  <si>
+    <t>备注</t>
   </si>
   <si>
     <t>收集数量目标</t>
@@ -155,6 +106,9 @@
     <t>MedalType</t>
   </si>
   <si>
+    <t>buildID</t>
+  </si>
+  <si>
     <t>CollectNum</t>
   </si>
   <si>
@@ -164,115 +118,100 @@
     <t>BuffStr</t>
   </si>
   <si>
-    <t>12405_100</t>
+    <t>愤怒的小鸟</t>
+  </si>
+  <si>
+    <t>1_100</t>
   </si>
   <si>
     <t>产出金币的所有房间收益：+(%s)/min</t>
   </si>
   <si>
-    <t>12404_100</t>
-  </si>
-  <si>
-    <t>[运营部]知名度上限：+(%s)</t>
-  </si>
-  <si>
-    <t>12406_1000</t>
-  </si>
-  <si>
-    <t>[营销部]曝光度上限：+(%s)</t>
-  </si>
-  <si>
-    <t>12408_100</t>
+    <t>1_150</t>
+  </si>
+  <si>
+    <t>1_200</t>
+  </si>
+  <si>
+    <t>1_250</t>
+  </si>
+  <si>
+    <t>1_300</t>
+  </si>
+  <si>
+    <t>1_350</t>
+  </si>
+  <si>
+    <t>象财神</t>
+  </si>
+  <si>
+    <t>6_100</t>
+  </si>
+  <si>
+    <t>[运营部]曝光度上限：+(%s)</t>
+  </si>
+  <si>
+    <t>6_150</t>
+  </si>
+  <si>
+    <t>6_200</t>
+  </si>
+  <si>
+    <t>6_250</t>
+  </si>
+  <si>
+    <t>6_300</t>
+  </si>
+  <si>
+    <t>6_350</t>
+  </si>
+  <si>
+    <t>超级明星</t>
+  </si>
+  <si>
+    <t>5_100</t>
+  </si>
+  <si>
+    <t>[营销部]知名度上限：+(%s)</t>
+  </si>
+  <si>
+    <t>5_150</t>
+  </si>
+  <si>
+    <t>5_200</t>
+  </si>
+  <si>
+    <t>5_250</t>
+  </si>
+  <si>
+    <t>5_300</t>
+  </si>
+  <si>
+    <t>5_350</t>
+  </si>
+  <si>
+    <t>财神来了</t>
+  </si>
+  <si>
+    <t>13_100</t>
   </si>
   <si>
     <t>[观看广告]金币收益：+(%s)</t>
   </si>
   <si>
-    <t>徽章ID</t>
-  </si>
-  <si>
-    <t>建筑ID</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>buildID</t>
-  </si>
-  <si>
-    <t>愤怒的小鸟</t>
-  </si>
-  <si>
-    <t>12405_150</t>
-  </si>
-  <si>
-    <t>12405_200</t>
-  </si>
-  <si>
-    <t>12405_250</t>
-  </si>
-  <si>
-    <t>12405_300</t>
-  </si>
-  <si>
-    <t>12405_350</t>
-  </si>
-  <si>
-    <t>象财神</t>
-  </si>
-  <si>
-    <t>12404_150</t>
-  </si>
-  <si>
-    <t>12404_200</t>
-  </si>
-  <si>
-    <t>12404_250</t>
-  </si>
-  <si>
-    <t>12404_300</t>
-  </si>
-  <si>
-    <t>12404_350</t>
-  </si>
-  <si>
-    <t>超级明星</t>
-  </si>
-  <si>
-    <t>12406_100</t>
-  </si>
-  <si>
-    <t>12406_150</t>
-  </si>
-  <si>
-    <t>12406_200</t>
-  </si>
-  <si>
-    <t>12406_250</t>
-  </si>
-  <si>
-    <t>12406_300</t>
-  </si>
-  <si>
-    <t>12406_350</t>
-  </si>
-  <si>
-    <t>财神来了</t>
-  </si>
-  <si>
-    <t>12408_150</t>
-  </si>
-  <si>
-    <t>12408_200</t>
-  </si>
-  <si>
-    <t>12408_250</t>
-  </si>
-  <si>
-    <t>12408_300</t>
-  </si>
-  <si>
-    <t>12408_350</t>
+    <t>13_150</t>
+  </si>
+  <si>
+    <t>13_200</t>
+  </si>
+  <si>
+    <t>13_250</t>
+  </si>
+  <si>
+    <t>13_300</t>
+  </si>
+  <si>
+    <t>13_350</t>
   </si>
   <si>
     <t>寒冰王座</t>
@@ -977,7 +916,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1031,9 +970,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1346,413 +1282,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="11.3166666666667" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.4333333333333" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="22.6416666666667" style="4" customWidth="1"/>
-    <col min="5" max="5" width="18.75" style="4" customWidth="1"/>
-    <col min="6" max="6" width="33.625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="17.3416666666667" style="4" customWidth="1"/>
-    <col min="8" max="8" width="11.125" style="4" customWidth="1"/>
-    <col min="9" max="9" width="18.675" style="4" customWidth="1"/>
-    <col min="10" max="10" width="43.75" style="4" customWidth="1"/>
-    <col min="11" max="11" width="15.625" style="4"/>
-    <col min="12" max="12" width="9.125" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="15.625" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="8"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="8"/>
-    </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-    </row>
-    <row r="5" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A5" s="11">
-        <v>101</v>
-      </c>
-      <c r="B5" s="11">
-        <v>2</v>
-      </c>
-      <c r="C5" s="11">
-        <v>3</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3">
-        <v>4060005</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A6" s="11">
-        <v>102</v>
-      </c>
-      <c r="B6" s="11">
-        <v>3</v>
-      </c>
-      <c r="C6" s="11">
-        <v>3</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="3">
-        <v>4060006</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="11"/>
-    </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A7" s="11">
-        <v>103</v>
-      </c>
-      <c r="B7" s="3">
-        <v>4</v>
-      </c>
-      <c r="C7" s="11">
-        <v>3</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="3">
-        <v>4060007</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="11"/>
-    </row>
-    <row r="8" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A8" s="11">
-        <v>104</v>
-      </c>
-      <c r="B8" s="3">
-        <v>5</v>
-      </c>
-      <c r="C8" s="11">
-        <v>3</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="3">
-        <v>4060008</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="12"/>
-    </row>
-    <row r="10" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="12"/>
-    </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-    </row>
-    <row r="12" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="13" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="12"/>
-    </row>
-    <row r="14" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-    </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="12"/>
-    </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="12"/>
-    </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-    </row>
-    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="12"/>
-    </row>
-    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="12"/>
-    </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="16"/>
-    </row>
-    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="17"/>
-    </row>
-    <row r="22" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="17"/>
-    </row>
-    <row r="23" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="18"/>
-    </row>
-    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="12"/>
-    </row>
-    <row r="25" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="12"/>
-    </row>
-    <row r="26" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-    </row>
-    <row r="27" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="12"/>
-    </row>
-    <row r="28" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="12"/>
-    </row>
-    <row r="29" s="3" customFormat="1" customHeight="1"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:L76"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
@@ -1776,25 +1305,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
@@ -1803,23 +1332,23 @@
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A2" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
@@ -1827,23 +1356,23 @@
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A3" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -1870,19 +1399,19 @@
         <v>1101</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E5" s="11">
         <v>5</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G5" s="3">
         <v>4060005</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" customHeight="1" spans="1:12">
@@ -1896,19 +1425,19 @@
         <v>1101</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E6" s="11">
         <v>15</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G6" s="3">
         <v>4060005</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L6" s="11"/>
     </row>
@@ -1923,19 +1452,19 @@
         <v>1101</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E7" s="11">
         <v>25</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3">
         <v>4060005</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L7" s="11"/>
     </row>
@@ -1950,19 +1479,19 @@
         <v>1101</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E8" s="11">
         <v>35</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3">
         <v>4060005</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" s="3" customFormat="1" customHeight="1" spans="1:12">
@@ -1976,19 +1505,19 @@
         <v>1101</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E9" s="11">
         <v>45</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G9" s="3">
         <v>4060005</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L9" s="12"/>
     </row>
@@ -2003,19 +1532,19 @@
         <v>1101</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E10" s="11">
         <v>50</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G10" s="3">
         <v>4060005</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L10" s="12"/>
     </row>
@@ -2030,19 +1559,19 @@
         <v>1102</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E11" s="11">
         <v>5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G11" s="3">
         <v>4060006</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" customHeight="1" spans="1:12">
@@ -2056,19 +1585,19 @@
         <v>1102</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E12" s="11">
         <v>15</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G12" s="3">
         <v>4060006</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="L12" s="12"/>
     </row>
@@ -2083,19 +1612,19 @@
         <v>1102</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E13" s="11">
         <v>25</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G13" s="3">
         <v>4060006</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="L13" s="12"/>
     </row>
@@ -2110,19 +1639,19 @@
         <v>1102</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E14" s="11">
         <v>35</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G14" s="3">
         <v>4060006</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" s="3" customFormat="1" customHeight="1" spans="1:12">
@@ -2136,19 +1665,19 @@
         <v>1102</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E15" s="11">
         <v>45</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G15" s="3">
         <v>4060006</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="L15" s="12"/>
     </row>
@@ -2163,19 +1692,19 @@
         <v>1102</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E16" s="11">
         <v>50</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3">
         <v>4060006</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="L16" s="12"/>
     </row>
@@ -2190,19 +1719,19 @@
         <v>1103</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E17" s="11">
         <v>5</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G17" s="3">
         <v>4060007</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
@@ -2219,19 +1748,19 @@
         <v>1103</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E18" s="11">
         <v>15</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G18" s="3">
         <v>4060007</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
@@ -2249,19 +1778,19 @@
         <v>1103</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E19" s="11">
         <v>25</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G19" s="3">
         <v>4060007</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14"/>
@@ -2279,19 +1808,19 @@
         <v>1103</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E20" s="11">
         <v>35</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G20" s="3">
         <v>4060007</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I20" s="15"/>
       <c r="J20" s="15"/>
@@ -2309,19 +1838,19 @@
         <v>1103</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E21" s="11">
         <v>45</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G21" s="3">
         <v>4060007</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I21" s="15"/>
       <c r="J21" s="15"/>
@@ -2339,19 +1868,19 @@
         <v>1103</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E22" s="11">
         <v>50</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G22" s="3">
         <v>4060007</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I22" s="15"/>
       <c r="J22" s="15"/>
@@ -2369,19 +1898,19 @@
         <v>1104</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E23" s="11">
         <v>5</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G23" s="3">
         <v>4060008</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="1:12">
@@ -2395,19 +1924,19 @@
         <v>1104</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E24" s="11">
         <v>15</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G24" s="3">
         <v>4060008</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="L24" s="12"/>
     </row>
@@ -2422,19 +1951,19 @@
         <v>1104</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E25" s="11">
         <v>25</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G25" s="3">
         <v>4060008</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="L25" s="12"/>
     </row>
@@ -2449,19 +1978,19 @@
         <v>1104</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E26" s="11">
         <v>35</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G26" s="3">
         <v>4060008</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" customHeight="1" spans="1:12">
@@ -2475,19 +2004,19 @@
         <v>1104</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E27" s="11">
         <v>45</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G27" s="3">
         <v>4060008</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="L27" s="12"/>
     </row>
@@ -2502,19 +2031,19 @@
         <v>1104</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E28" s="11">
         <v>50</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G28" s="3">
         <v>4060008</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="L28" s="12"/>
     </row>
@@ -2529,19 +2058,19 @@
         <v>1105</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E29" s="11">
         <v>5</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G29" s="3">
         <v>4060005</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:12">
@@ -2555,19 +2084,19 @@
         <v>1105</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E30" s="11">
         <v>15</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G30" s="3">
         <v>4060005</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:12">
@@ -2581,19 +2110,19 @@
         <v>1105</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E31" s="11">
         <v>25</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G31" s="3">
         <v>4060005</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:12">
@@ -2607,19 +2136,19 @@
         <v>1105</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E32" s="11">
         <v>35</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G32" s="3">
         <v>4060005</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:8">
@@ -2633,19 +2162,19 @@
         <v>1105</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E33" s="11">
         <v>45</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G33" s="3">
         <v>4060005</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:8">
@@ -2659,19 +2188,19 @@
         <v>1105</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E34" s="11">
         <v>50</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G34" s="3">
         <v>4060005</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:8">
@@ -2685,24 +2214,24 @@
         <v>1106</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E35" s="11">
         <v>5</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G35" s="3">
         <v>4060006</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:8">
       <c r="A36" s="4">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B36" s="4">
         <v>6</v>
@@ -2711,24 +2240,24 @@
         <v>1106</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E36" s="11">
         <v>15</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G36" s="3">
         <v>4060006</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:8">
       <c r="A37" s="4">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B37" s="4">
         <v>6</v>
@@ -2737,24 +2266,24 @@
         <v>1106</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E37" s="11">
         <v>25</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G37" s="3">
         <v>4060006</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:8">
       <c r="A38" s="4">
-        <v>1501</v>
+        <v>1504</v>
       </c>
       <c r="B38" s="4">
         <v>6</v>
@@ -2763,24 +2292,24 @@
         <v>1106</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E38" s="11">
         <v>35</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G38" s="3">
         <v>4060006</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:8">
       <c r="A39" s="4">
-        <v>1501</v>
+        <v>1505</v>
       </c>
       <c r="B39" s="4">
         <v>6</v>
@@ -2789,24 +2318,24 @@
         <v>1106</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E39" s="11">
         <v>45</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G39" s="3">
         <v>4060006</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:8">
       <c r="A40" s="4">
-        <v>1501</v>
+        <v>1506</v>
       </c>
       <c r="B40" s="4">
         <v>6</v>
@@ -2815,19 +2344,19 @@
         <v>1106</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E40" s="11">
         <v>50</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G40" s="3">
         <v>4060006</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:8">
@@ -2841,19 +2370,19 @@
         <v>1107</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E41" s="11">
         <v>5</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G41" s="3">
         <v>4060007</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:8">
@@ -2867,19 +2396,19 @@
         <v>1107</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E42" s="11">
         <v>15</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G42" s="3">
         <v>4060007</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:8">
@@ -2893,19 +2422,19 @@
         <v>1107</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E43" s="11">
         <v>25</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G43" s="3">
         <v>4060007</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:8">
@@ -2919,19 +2448,19 @@
         <v>1107</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E44" s="11">
         <v>35</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G44" s="3">
         <v>4060007</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:8">
@@ -2945,19 +2474,19 @@
         <v>1107</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E45" s="11">
         <v>45</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G45" s="3">
         <v>4060007</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:8">
@@ -2971,19 +2500,19 @@
         <v>1107</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E46" s="11">
         <v>50</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G46" s="3">
         <v>4060007</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:8">
@@ -2997,19 +2526,19 @@
         <v>1108</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E47" s="11">
         <v>5</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G47" s="3">
         <v>4060008</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:8">
@@ -3023,19 +2552,19 @@
         <v>1108</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E48" s="11">
         <v>15</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G48" s="3">
         <v>4060008</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:8">
@@ -3049,19 +2578,19 @@
         <v>1108</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E49" s="11">
         <v>25</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G49" s="3">
         <v>4060008</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:8">
@@ -3075,19 +2604,19 @@
         <v>1108</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E50" s="11">
         <v>35</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G50" s="3">
         <v>4060008</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:8">
@@ -3101,19 +2630,19 @@
         <v>1108</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E51" s="11">
         <v>45</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G51" s="3">
         <v>4060008</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:8">
@@ -3127,19 +2656,19 @@
         <v>1108</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E52" s="11">
         <v>50</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G52" s="3">
         <v>4060008</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:8">
@@ -3153,19 +2682,19 @@
         <v>1109</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E53" s="11">
         <v>5</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G53" s="3">
         <v>4060005</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:8">
@@ -3179,19 +2708,19 @@
         <v>1109</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E54" s="11">
         <v>15</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G54" s="3">
         <v>4060005</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:8">
@@ -3205,19 +2734,19 @@
         <v>1109</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E55" s="11">
         <v>25</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G55" s="3">
         <v>4060005</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:8">
@@ -3231,19 +2760,19 @@
         <v>1109</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E56" s="11">
         <v>35</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G56" s="3">
         <v>4060005</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:8">
@@ -3257,19 +2786,19 @@
         <v>1109</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E57" s="11">
         <v>45</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="G57" s="3">
         <v>4060005</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:8">
@@ -3283,19 +2812,19 @@
         <v>1109</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E58" s="11">
         <v>50</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G58" s="3">
         <v>4060005</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:8">
@@ -3309,19 +2838,19 @@
         <v>1110</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E59" s="11">
         <v>5</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G59" s="3">
         <v>4060006</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:8">
@@ -3335,19 +2864,19 @@
         <v>1110</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E60" s="11">
         <v>15</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G60" s="3">
         <v>4060006</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:8">
@@ -3361,19 +2890,19 @@
         <v>1110</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E61" s="11">
         <v>25</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G61" s="3">
         <v>4060006</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:8">
@@ -3387,19 +2916,19 @@
         <v>1110</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E62" s="11">
         <v>35</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G62" s="3">
         <v>4060006</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:8">
@@ -3413,19 +2942,19 @@
         <v>1110</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E63" s="11">
         <v>45</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G63" s="3">
         <v>4060006</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:8">
@@ -3439,19 +2968,19 @@
         <v>1110</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E64" s="11">
         <v>50</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G64" s="3">
         <v>4060006</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:8">
@@ -3465,19 +2994,19 @@
         <v>1111</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E65" s="11">
         <v>5</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G65" s="3">
         <v>4060007</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:8">
@@ -3491,19 +3020,19 @@
         <v>1111</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E66" s="11">
         <v>15</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G66" s="3">
         <v>4060007</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:8">
@@ -3517,19 +3046,19 @@
         <v>1111</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E67" s="11">
         <v>25</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G67" s="3">
         <v>4060007</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:8">
@@ -3543,19 +3072,19 @@
         <v>1111</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E68" s="11">
         <v>35</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G68" s="3">
         <v>4060007</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="1:8">
@@ -3569,19 +3098,19 @@
         <v>1111</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E69" s="11">
         <v>45</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G69" s="3">
         <v>4060007</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:8">
@@ -3595,19 +3124,19 @@
         <v>1111</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E70" s="11">
         <v>50</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G70" s="3">
         <v>4060007</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:8">
@@ -3621,19 +3150,19 @@
         <v>1112</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E71" s="11">
         <v>5</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="G71" s="3">
         <v>4060008</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:8">
@@ -3647,19 +3176,19 @@
         <v>1112</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E72" s="11">
         <v>15</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G72" s="3">
         <v>4060008</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:8">
@@ -3673,19 +3202,19 @@
         <v>1112</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E73" s="11">
         <v>25</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G73" s="3">
         <v>4060008</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:8">
@@ -3699,19 +3228,19 @@
         <v>1112</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E74" s="11">
         <v>35</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G74" s="3">
         <v>4060008</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:8">
@@ -3725,19 +3254,19 @@
         <v>1112</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E75" s="11">
         <v>45</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G75" s="3">
         <v>4060008</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:8">
@@ -3751,19 +3280,19 @@
         <v>1112</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E76" s="11">
         <v>50</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G76" s="3">
         <v>4060008</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -3774,7 +3303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>

--- a/hall/resources/sample/MedalBuff.xlsx
+++ b/hall/resources/sample/MedalBuff.xlsx
@@ -38,7 +38,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="66">
   <si>
     <t>序号</t>
   </si>
@@ -73,6 +73,9 @@
     <t>徽章ID</t>
   </si>
   <si>
+    <t>徽章名称</t>
+  </si>
+  <si>
     <t>建筑ID</t>
   </si>
   <si>
@@ -106,6 +109,9 @@
     <t>MedalType</t>
   </si>
   <si>
+    <t>nameid</t>
+  </si>
+  <si>
     <t>buildID</t>
   </si>
   <si>
@@ -236,6 +242,27 @@
   </si>
   <si>
     <t>杰克船长</t>
+  </si>
+  <si>
+    <t>打卡卫士</t>
+  </si>
+  <si>
+    <t>1_50</t>
+  </si>
+  <si>
+    <t>成长之路</t>
+  </si>
+  <si>
+    <t>建筑能手</t>
+  </si>
+  <si>
+    <t>广告精英</t>
+  </si>
+  <si>
+    <t>招商能手</t>
+  </si>
+  <si>
+    <t>游戏大亨</t>
   </si>
 </sst>
 </file>
@@ -449,12 +476,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -916,7 +943,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -969,6 +996,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1023,6 +1053,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="9" tint="0.4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1282,25 +1321,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.3166666666667" style="4" customWidth="1"/>
-    <col min="2" max="3" width="15.4333333333333" style="4" customWidth="1"/>
-    <col min="4" max="5" width="13.875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="22.6416666666667" style="4" customWidth="1"/>
-    <col min="7" max="7" width="18.75" style="4" customWidth="1"/>
-    <col min="8" max="8" width="33.625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="17.3416666666667" style="4" customWidth="1"/>
-    <col min="10" max="10" width="11.125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="18.675" style="4" customWidth="1"/>
-    <col min="12" max="12" width="43.75" style="4" customWidth="1"/>
-    <col min="13" max="13" width="15.625" style="4"/>
-    <col min="14" max="14" width="9.125" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="15.625" style="4"/>
+    <col min="2" max="4" width="15.4333333333333" style="4" customWidth="1"/>
+    <col min="5" max="6" width="13.875" style="4" customWidth="1"/>
+    <col min="7" max="7" width="22.6416666666667" style="4" customWidth="1"/>
+    <col min="8" max="8" width="18.75" style="4" customWidth="1"/>
+    <col min="9" max="9" width="33.625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="17.3416666666667" style="4" customWidth="1"/>
+    <col min="11" max="11" width="11.125" style="4" customWidth="1"/>
+    <col min="12" max="12" width="18.675" style="4" customWidth="1"/>
+    <col min="13" max="13" width="43.75" style="4" customWidth="1"/>
+    <col min="14" max="14" width="15.625" style="4"/>
+    <col min="15" max="15" width="9.125" style="4" customWidth="1"/>
+    <col min="16" max="16384" width="15.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1319,76 +1358,86 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7"/>
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
-      <c r="L1" s="8"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L1" s="7"/>
+      <c r="M1" s="8"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="7"/>
+      <c r="H2" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="K2" s="7"/>
-      <c r="L2" s="8"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L2" s="7"/>
+      <c r="M2" s="8"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
         <v>14</v>
       </c>
+      <c r="D3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="G3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="8"/>
-    </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L3" s="7"/>
+      <c r="M3" s="8"/>
+    </row>
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:13">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
-    </row>
-    <row r="5" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="G4" s="10"/>
+    </row>
+    <row r="5" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A5" s="11">
         <v>1001</v>
       </c>
@@ -1396,25 +1445,28 @@
         <v>1</v>
       </c>
       <c r="C5" s="11">
+        <v>103900001</v>
+      </c>
+      <c r="D5" s="11">
         <v>1101</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="11">
+      <c r="E5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="11">
         <v>5</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="3">
+      <c r="G5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="3">
         <v>4060005</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A6" s="11">
         <v>1002</v>
       </c>
@@ -1422,26 +1474,29 @@
         <v>1</v>
       </c>
       <c r="C6" s="11">
+        <v>103900001</v>
+      </c>
+      <c r="D6" s="11">
         <v>1101</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="11">
+      <c r="E6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="11">
         <v>15</v>
       </c>
-      <c r="F6" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="G6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="3">
         <v>4060005</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" s="11"/>
-    </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M6" s="11"/>
+    </row>
+    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A7" s="11">
         <v>1003</v>
       </c>
@@ -1449,26 +1504,29 @@
         <v>1</v>
       </c>
       <c r="C7" s="11">
+        <v>103900001</v>
+      </c>
+      <c r="D7" s="11">
         <v>1101</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="11">
+      <c r="E7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="11">
         <v>25</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="G7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="3">
-        <v>4060005</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" s="11"/>
-    </row>
-    <row r="8" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M7" s="11"/>
+    </row>
+    <row r="8" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A8" s="11">
         <v>1004</v>
       </c>
@@ -1476,25 +1534,28 @@
         <v>1</v>
       </c>
       <c r="C8" s="11">
+        <v>103900001</v>
+      </c>
+      <c r="D8" s="11">
         <v>1101</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="11">
+      <c r="E8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="11">
         <v>35</v>
       </c>
-      <c r="F8" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="G8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="3">
         <v>4060005</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I8" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A9" s="11">
         <v>1005</v>
       </c>
@@ -1502,26 +1563,29 @@
         <v>1</v>
       </c>
       <c r="C9" s="11">
+        <v>103900001</v>
+      </c>
+      <c r="D9" s="11">
         <v>1101</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="11">
+      <c r="E9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="11">
         <v>45</v>
       </c>
-      <c r="F9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="G9" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="3">
         <v>4060005</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="12"/>
-    </row>
-    <row r="10" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="12"/>
+    </row>
+    <row r="10" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A10" s="11">
         <v>1006</v>
       </c>
@@ -1529,26 +1593,29 @@
         <v>1</v>
       </c>
       <c r="C10" s="11">
+        <v>103900001</v>
+      </c>
+      <c r="D10" s="11">
         <v>1101</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="11">
+      <c r="E10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="11">
         <v>50</v>
       </c>
-      <c r="F10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="G10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="3">
         <v>4060005</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" s="12"/>
-    </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M10" s="12"/>
+    </row>
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A11" s="11">
         <v>1101</v>
       </c>
@@ -1556,25 +1623,28 @@
         <v>2</v>
       </c>
       <c r="C11" s="11">
+        <v>102700001</v>
+      </c>
+      <c r="D11" s="11">
         <v>1102</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="11">
+      <c r="E11" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="11">
         <v>5</v>
       </c>
-      <c r="F11" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="G11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" s="3">
         <v>4060006</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I11" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A12" s="11">
         <v>1102</v>
       </c>
@@ -1582,26 +1652,29 @@
         <v>2</v>
       </c>
       <c r="C12" s="11">
+        <v>102700001</v>
+      </c>
+      <c r="D12" s="11">
         <v>1102</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="11">
+      <c r="E12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="11">
         <v>15</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="G12" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="3">
         <v>4060006</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" s="12"/>
-    </row>
-    <row r="13" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="12"/>
+    </row>
+    <row r="13" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A13" s="11">
         <v>1103</v>
       </c>
@@ -1609,26 +1682,29 @@
         <v>2</v>
       </c>
       <c r="C13" s="11">
+        <v>102700001</v>
+      </c>
+      <c r="D13" s="11">
         <v>1102</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="11">
         <v>25</v>
       </c>
-      <c r="E13" s="11">
-        <v>25</v>
-      </c>
-      <c r="F13" s="11" t="s">
+      <c r="G13" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="3">
-        <v>4060006</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L13" s="12"/>
-    </row>
-    <row r="14" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A14" s="11">
         <v>1104</v>
       </c>
@@ -1636,25 +1712,28 @@
         <v>2</v>
       </c>
       <c r="C14" s="11">
+        <v>102700001</v>
+      </c>
+      <c r="D14" s="11">
         <v>1102</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="11">
+      <c r="E14" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="11">
         <v>35</v>
       </c>
-      <c r="F14" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="3">
         <v>4060006</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I14" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A15" s="11">
         <v>1105</v>
       </c>
@@ -1662,26 +1741,29 @@
         <v>2</v>
       </c>
       <c r="C15" s="11">
+        <v>102700001</v>
+      </c>
+      <c r="D15" s="11">
         <v>1102</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="11">
+      <c r="E15" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F15" s="11">
         <v>45</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="G15" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="3">
         <v>4060006</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" s="12"/>
-    </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A16" s="11">
         <v>1106</v>
       </c>
@@ -1689,26 +1771,29 @@
         <v>2</v>
       </c>
       <c r="C16" s="11">
+        <v>102700001</v>
+      </c>
+      <c r="D16" s="11">
         <v>1102</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="11">
+      <c r="E16" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F16" s="11">
         <v>50</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="G16" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="3">
         <v>4060006</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" s="12"/>
-    </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M16" s="12"/>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A17" s="13">
         <v>1201</v>
       </c>
@@ -1716,28 +1801,31 @@
         <v>3</v>
       </c>
       <c r="C17" s="13">
+        <v>100300001</v>
+      </c>
+      <c r="D17" s="13">
         <v>1103</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="11">
+      <c r="E17" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="11">
         <v>5</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="3">
+      <c r="G17" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="3">
         <v>4060007</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" s="14"/>
+      <c r="I17" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="J17" s="14"/>
       <c r="K17" s="14"/>
-    </row>
-    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L17" s="14"/>
+    </row>
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A18" s="13">
         <v>1202</v>
       </c>
@@ -1745,29 +1833,32 @@
         <v>3</v>
       </c>
       <c r="C18" s="13">
+        <v>100300001</v>
+      </c>
+      <c r="D18" s="13">
         <v>1103</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="11">
+      <c r="E18" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="11">
         <v>15</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="G18" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" s="3">
         <v>4060007</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" s="14"/>
+      <c r="I18" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="J18" s="14"/>
       <c r="K18" s="14"/>
-      <c r="L18" s="12"/>
-    </row>
-    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L18" s="14"/>
+      <c r="M18" s="12"/>
+    </row>
+    <row r="19" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A19" s="13">
         <v>1203</v>
       </c>
@@ -1775,29 +1866,32 @@
         <v>3</v>
       </c>
       <c r="C19" s="13">
+        <v>100300001</v>
+      </c>
+      <c r="D19" s="13">
         <v>1103</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" s="11">
+      <c r="E19" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="11">
         <v>25</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="G19" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G19" s="3">
-        <v>4060007</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" s="14"/>
       <c r="J19" s="14"/>
       <c r="K19" s="14"/>
-      <c r="L19" s="12"/>
-    </row>
-    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L19" s="14"/>
+      <c r="M19" s="12"/>
+    </row>
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A20" s="13">
         <v>1204</v>
       </c>
@@ -1805,29 +1899,32 @@
         <v>3</v>
       </c>
       <c r="C20" s="13">
+        <v>100300001</v>
+      </c>
+      <c r="D20" s="13">
         <v>1103</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="11">
+      <c r="E20" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F20" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="F20" s="11">
+        <v>35</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="3">
         <v>4060007</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="15"/>
+      <c r="I20" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
-      <c r="L20" s="16"/>
-    </row>
-    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L20" s="15"/>
+      <c r="M20" s="16"/>
+    </row>
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A21" s="13">
         <v>1205</v>
       </c>
@@ -1835,29 +1932,32 @@
         <v>3</v>
       </c>
       <c r="C21" s="13">
+        <v>100300001</v>
+      </c>
+      <c r="D21" s="13">
         <v>1103</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="11">
+      <c r="E21" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" s="11">
         <v>45</v>
       </c>
-      <c r="F21" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="G21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H21" s="3">
         <v>4060007</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I21" s="15"/>
+      <c r="I21" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="J21" s="15"/>
       <c r="K21" s="15"/>
-      <c r="L21" s="17"/>
-    </row>
-    <row r="22" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L21" s="15"/>
+      <c r="M21" s="17"/>
+    </row>
+    <row r="22" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A22" s="13">
         <v>1206</v>
       </c>
@@ -1865,29 +1965,32 @@
         <v>3</v>
       </c>
       <c r="C22" s="13">
+        <v>100300001</v>
+      </c>
+      <c r="D22" s="13">
         <v>1103</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="11">
+      <c r="E22" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="11">
         <v>50</v>
       </c>
-      <c r="F22" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="G22" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="3">
         <v>4060007</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" s="15"/>
+      <c r="I22" s="3" t="s">
+        <v>37</v>
+      </c>
       <c r="J22" s="15"/>
       <c r="K22" s="15"/>
-      <c r="L22" s="17"/>
-    </row>
-    <row r="23" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="L22" s="15"/>
+      <c r="M22" s="17"/>
+    </row>
+    <row r="23" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A23" s="11">
         <v>1301</v>
       </c>
@@ -1895,25 +1998,28 @@
         <v>4</v>
       </c>
       <c r="C23" s="11">
+        <v>101200001</v>
+      </c>
+      <c r="D23" s="11">
         <v>1104</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="11">
+      <c r="E23" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="11">
         <v>5</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="G23" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="3">
         <v>4060008</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I23" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A24" s="11">
         <v>1302</v>
       </c>
@@ -1921,26 +2027,29 @@
         <v>4</v>
       </c>
       <c r="C24" s="11">
+        <v>101200001</v>
+      </c>
+      <c r="D24" s="11">
         <v>1104</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="11">
+      <c r="E24" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="11">
         <v>15</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="G24" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="3">
         <v>4060008</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L24" s="12"/>
-    </row>
-    <row r="25" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M24" s="12"/>
+    </row>
+    <row r="25" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A25" s="11">
         <v>1303</v>
       </c>
@@ -1948,26 +2057,29 @@
         <v>4</v>
       </c>
       <c r="C25" s="11">
+        <v>101200001</v>
+      </c>
+      <c r="D25" s="11">
         <v>1104</v>
       </c>
-      <c r="D25" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="11">
+      <c r="E25" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="11">
         <v>25</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="G25" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H25" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="3">
-        <v>4060008</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L25" s="12"/>
-    </row>
-    <row r="26" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="M25" s="12"/>
+    </row>
+    <row r="26" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A26" s="11">
         <v>1304</v>
       </c>
@@ -1975,25 +2087,28 @@
         <v>4</v>
       </c>
       <c r="C26" s="11">
+        <v>101200001</v>
+      </c>
+      <c r="D26" s="11">
         <v>1104</v>
       </c>
-      <c r="D26" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="11">
+      <c r="E26" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="11">
         <v>35</v>
       </c>
-      <c r="F26" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="G26" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H26" s="3">
         <v>4060008</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I26" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A27" s="11">
         <v>1305</v>
       </c>
@@ -2001,26 +2116,29 @@
         <v>4</v>
       </c>
       <c r="C27" s="11">
+        <v>101200001</v>
+      </c>
+      <c r="D27" s="11">
         <v>1104</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="11">
+      <c r="E27" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="11">
         <v>45</v>
       </c>
-      <c r="F27" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="G27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" s="3">
         <v>4060008</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L27" s="12"/>
-    </row>
-    <row r="28" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M27" s="12"/>
+    </row>
+    <row r="28" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A28" s="11">
         <v>1306</v>
       </c>
@@ -2028,26 +2146,29 @@
         <v>4</v>
       </c>
       <c r="C28" s="11">
+        <v>101200001</v>
+      </c>
+      <c r="D28" s="11">
         <v>1104</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="11">
+      <c r="E28" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" s="11">
         <v>50</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G28" s="3">
+      <c r="G28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" s="3">
         <v>4060008</v>
       </c>
-      <c r="H28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L28" s="12"/>
-    </row>
-    <row r="29" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="I28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M28" s="12"/>
+    </row>
+    <row r="29" s="3" customFormat="1" customHeight="1" spans="1:13">
       <c r="A29" s="3">
         <v>1401</v>
       </c>
@@ -2055,25 +2176,28 @@
         <v>5</v>
       </c>
       <c r="C29" s="3">
+        <v>102500001</v>
+      </c>
+      <c r="D29" s="3">
         <v>1105</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" s="11">
+      <c r="E29" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="11">
         <v>5</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="3">
+      <c r="G29" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="3">
         <v>4060005</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:12">
+      <c r="I29" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:13">
       <c r="A30" s="3">
         <v>1402</v>
       </c>
@@ -2081,25 +2205,28 @@
         <v>5</v>
       </c>
       <c r="C30" s="3">
+        <v>102500001</v>
+      </c>
+      <c r="D30" s="3">
         <v>1105</v>
       </c>
-      <c r="D30" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" s="11">
+      <c r="E30" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F30" s="11">
         <v>15</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" s="3">
+      <c r="G30" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="3">
         <v>4060005</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:12">
+      <c r="I30" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:13">
       <c r="A31" s="3">
         <v>1403</v>
       </c>
@@ -2107,25 +2234,28 @@
         <v>5</v>
       </c>
       <c r="C31" s="3">
+        <v>102500001</v>
+      </c>
+      <c r="D31" s="3">
         <v>1105</v>
       </c>
-      <c r="D31" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" s="11">
+      <c r="E31" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="11">
         <v>25</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="G31" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G31" s="3">
-        <v>4060005</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="1:12">
+    </row>
+    <row r="32" customHeight="1" spans="1:13">
       <c r="A32" s="3">
         <v>1404</v>
       </c>
@@ -2133,25 +2263,28 @@
         <v>5</v>
       </c>
       <c r="C32" s="3">
+        <v>102500001</v>
+      </c>
+      <c r="D32" s="3">
         <v>1105</v>
       </c>
-      <c r="D32" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" s="11">
+      <c r="E32" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="11">
         <v>35</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="3">
         <v>4060005</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:8">
+      <c r="I32" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:9">
       <c r="A33" s="3">
         <v>1405</v>
       </c>
@@ -2159,25 +2292,28 @@
         <v>5</v>
       </c>
       <c r="C33" s="3">
+        <v>102500001</v>
+      </c>
+      <c r="D33" s="3">
         <v>1105</v>
       </c>
-      <c r="D33" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E33" s="11">
+      <c r="E33" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F33" s="11">
         <v>45</v>
       </c>
-      <c r="F33" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G33" s="3">
+      <c r="G33" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H33" s="3">
         <v>4060005</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:8">
+      <c r="I33" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:9">
       <c r="A34" s="3">
         <v>1406</v>
       </c>
@@ -2185,25 +2321,28 @@
         <v>5</v>
       </c>
       <c r="C34" s="3">
+        <v>102500001</v>
+      </c>
+      <c r="D34" s="3">
         <v>1105</v>
       </c>
-      <c r="D34" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="11">
+      <c r="E34" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="F34" s="11">
         <v>50</v>
       </c>
-      <c r="F34" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" s="3">
+      <c r="G34" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="3">
         <v>4060005</v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:8">
+      <c r="I34" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:9">
       <c r="A35" s="4">
         <v>1501</v>
       </c>
@@ -2211,25 +2350,28 @@
         <v>6</v>
       </c>
       <c r="C35" s="4">
+        <v>103100001</v>
+      </c>
+      <c r="D35" s="4">
         <v>1106</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="11">
+      <c r="E35" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" s="11">
         <v>5</v>
       </c>
-      <c r="F35" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="G35" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H35" s="3">
         <v>4060006</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="1:8">
+      <c r="I35" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:9">
       <c r="A36" s="4">
         <v>1502</v>
       </c>
@@ -2237,25 +2379,28 @@
         <v>6</v>
       </c>
       <c r="C36" s="4">
+        <v>103100001</v>
+      </c>
+      <c r="D36" s="4">
         <v>1106</v>
       </c>
-      <c r="D36" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" s="11">
+      <c r="E36" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F36" s="11">
         <v>15</v>
       </c>
-      <c r="F36" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G36" s="3">
+      <c r="G36" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H36" s="3">
         <v>4060006</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="1:8">
+      <c r="I36" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:9">
       <c r="A37" s="4">
         <v>1503</v>
       </c>
@@ -2263,25 +2408,28 @@
         <v>6</v>
       </c>
       <c r="C37" s="4">
+        <v>103100001</v>
+      </c>
+      <c r="D37" s="4">
         <v>1106</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E37" s="11">
+      <c r="E37" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F37" s="11">
         <v>25</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="G37" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G37" s="3">
-        <v>4060006</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="1:8">
+    </row>
+    <row r="38" customHeight="1" spans="1:9">
       <c r="A38" s="4">
         <v>1504</v>
       </c>
@@ -2289,25 +2437,28 @@
         <v>6</v>
       </c>
       <c r="C38" s="4">
+        <v>103100001</v>
+      </c>
+      <c r="D38" s="4">
         <v>1106</v>
       </c>
-      <c r="D38" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E38" s="11">
+      <c r="E38" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" s="11">
         <v>35</v>
       </c>
-      <c r="F38" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G38" s="3">
+      <c r="G38" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H38" s="3">
         <v>4060006</v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="1:8">
+      <c r="I38" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:9">
       <c r="A39" s="4">
         <v>1505</v>
       </c>
@@ -2315,25 +2466,28 @@
         <v>6</v>
       </c>
       <c r="C39" s="4">
+        <v>103100001</v>
+      </c>
+      <c r="D39" s="4">
         <v>1106</v>
       </c>
-      <c r="D39" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="11">
+      <c r="E39" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F39" s="11">
         <v>45</v>
       </c>
-      <c r="F39" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G39" s="3">
+      <c r="G39" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H39" s="3">
         <v>4060006</v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="1:8">
+      <c r="I39" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:9">
       <c r="A40" s="4">
         <v>1506</v>
       </c>
@@ -2341,25 +2495,28 @@
         <v>6</v>
       </c>
       <c r="C40" s="4">
+        <v>103100001</v>
+      </c>
+      <c r="D40" s="4">
         <v>1106</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="E40" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="11">
         <v>50</v>
       </c>
-      <c r="E40" s="11">
-        <v>50</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G40" s="3">
+      <c r="G40" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" s="3">
         <v>4060006</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:8">
+      <c r="I40" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:9">
       <c r="A41" s="4">
         <v>1601</v>
       </c>
@@ -2367,25 +2524,28 @@
         <v>7</v>
       </c>
       <c r="C41" s="4">
+        <v>101800001</v>
+      </c>
+      <c r="D41" s="4">
         <v>1107</v>
       </c>
-      <c r="D41" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E41" s="11">
+      <c r="E41" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" s="11">
         <v>5</v>
       </c>
-      <c r="F41" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H41" s="3">
         <v>4060007</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:8">
+      <c r="I41" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:9">
       <c r="A42" s="4">
         <v>1602</v>
       </c>
@@ -2393,25 +2553,28 @@
         <v>7</v>
       </c>
       <c r="C42" s="4">
+        <v>101800001</v>
+      </c>
+      <c r="D42" s="4">
         <v>1107</v>
       </c>
-      <c r="D42" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="11">
+      <c r="E42" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42" s="11">
         <v>15</v>
       </c>
-      <c r="F42" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="G42" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H42" s="3">
         <v>4060007</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="1:8">
+      <c r="I42" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:9">
       <c r="A43" s="4">
         <v>1603</v>
       </c>
@@ -2419,25 +2582,28 @@
         <v>7</v>
       </c>
       <c r="C43" s="4">
+        <v>101800001</v>
+      </c>
+      <c r="D43" s="4">
         <v>1107</v>
       </c>
-      <c r="D43" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E43" s="11">
+      <c r="E43" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F43" s="11">
         <v>25</v>
       </c>
-      <c r="F43" s="11" t="s">
+      <c r="G43" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H43" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G43" s="3">
-        <v>4060007</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="1:8">
+    </row>
+    <row r="44" customHeight="1" spans="1:9">
       <c r="A44" s="4">
         <v>1604</v>
       </c>
@@ -2445,25 +2611,28 @@
         <v>7</v>
       </c>
       <c r="C44" s="4">
+        <v>101800001</v>
+      </c>
+      <c r="D44" s="4">
         <v>1107</v>
       </c>
-      <c r="D44" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="11">
+      <c r="E44" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F44" s="11">
         <v>35</v>
       </c>
-      <c r="F44" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="G44" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H44" s="3">
         <v>4060007</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="1:8">
+      <c r="I44" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:9">
       <c r="A45" s="4">
         <v>1605</v>
       </c>
@@ -2471,25 +2640,28 @@
         <v>7</v>
       </c>
       <c r="C45" s="4">
+        <v>101800001</v>
+      </c>
+      <c r="D45" s="4">
         <v>1107</v>
       </c>
-      <c r="D45" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" s="11">
+      <c r="E45" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" s="11">
         <v>45</v>
       </c>
-      <c r="F45" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H45" s="3">
         <v>4060007</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="1:8">
+      <c r="I45" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:9">
       <c r="A46" s="4">
         <v>1606</v>
       </c>
@@ -2497,25 +2669,28 @@
         <v>7</v>
       </c>
       <c r="C46" s="4">
+        <v>101800001</v>
+      </c>
+      <c r="D46" s="4">
         <v>1107</v>
       </c>
-      <c r="D46" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="E46" s="11">
+      <c r="E46" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="11">
         <v>50</v>
       </c>
-      <c r="F46" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H46" s="3">
         <v>4060007</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="1:8">
+      <c r="I46" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:9">
       <c r="A47" s="4">
         <v>1701</v>
       </c>
@@ -2523,25 +2698,28 @@
         <v>8</v>
       </c>
       <c r="C47" s="4">
+        <v>102000001</v>
+      </c>
+      <c r="D47" s="4">
         <v>1108</v>
       </c>
-      <c r="D47" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E47" s="11">
+      <c r="E47" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F47" s="11">
         <v>5</v>
       </c>
-      <c r="F47" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H47" s="3">
         <v>4060008</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="1:8">
+      <c r="I47" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:9">
       <c r="A48" s="4">
         <v>1702</v>
       </c>
@@ -2549,25 +2727,28 @@
         <v>8</v>
       </c>
       <c r="C48" s="4">
+        <v>102000001</v>
+      </c>
+      <c r="D48" s="4">
         <v>1108</v>
       </c>
-      <c r="D48" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E48" s="11">
+      <c r="E48" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F48" s="11">
         <v>15</v>
       </c>
-      <c r="F48" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H48" s="3">
         <v>4060008</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" customHeight="1" spans="1:8">
+      <c r="I48" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:9">
       <c r="A49" s="4">
         <v>1703</v>
       </c>
@@ -2575,25 +2756,28 @@
         <v>8</v>
       </c>
       <c r="C49" s="4">
+        <v>102000001</v>
+      </c>
+      <c r="D49" s="4">
         <v>1108</v>
       </c>
-      <c r="D49" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E49" s="11">
+      <c r="E49" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F49" s="11">
         <v>25</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="G49" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G49" s="3">
-        <v>4060008</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="50" customHeight="1" spans="1:8">
+    </row>
+    <row r="50" customHeight="1" spans="1:9">
       <c r="A50" s="4">
         <v>1704</v>
       </c>
@@ -2601,25 +2785,28 @@
         <v>8</v>
       </c>
       <c r="C50" s="4">
+        <v>102000001</v>
+      </c>
+      <c r="D50" s="4">
         <v>1108</v>
       </c>
-      <c r="D50" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E50" s="11">
+      <c r="E50" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F50" s="11">
         <v>35</v>
       </c>
-      <c r="F50" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G50" s="3">
+      <c r="G50" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H50" s="3">
         <v>4060008</v>
       </c>
-      <c r="H50" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="1:8">
+      <c r="I50" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:9">
       <c r="A51" s="4">
         <v>1705</v>
       </c>
@@ -2627,25 +2814,28 @@
         <v>8</v>
       </c>
       <c r="C51" s="4">
+        <v>102000001</v>
+      </c>
+      <c r="D51" s="4">
         <v>1108</v>
       </c>
-      <c r="D51" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" s="11">
+      <c r="E51" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F51" s="11">
         <v>45</v>
       </c>
-      <c r="F51" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G51" s="3">
+      <c r="G51" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H51" s="3">
         <v>4060008</v>
       </c>
-      <c r="H51" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="1:8">
+      <c r="I51" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:9">
       <c r="A52" s="4">
         <v>1706</v>
       </c>
@@ -2653,25 +2843,28 @@
         <v>8</v>
       </c>
       <c r="C52" s="4">
+        <v>102000001</v>
+      </c>
+      <c r="D52" s="4">
         <v>1108</v>
       </c>
-      <c r="D52" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E52" s="11">
+      <c r="E52" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F52" s="11">
         <v>50</v>
       </c>
-      <c r="F52" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="G52" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H52" s="3">
         <v>4060008</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="1:8">
+      <c r="I52" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:9">
       <c r="A53" s="4">
         <v>1801</v>
       </c>
@@ -2679,25 +2872,28 @@
         <v>9</v>
       </c>
       <c r="C53" s="4">
+        <v>101500001</v>
+      </c>
+      <c r="D53" s="4">
         <v>1109</v>
       </c>
-      <c r="D53" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E53" s="11">
+      <c r="E53" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F53" s="11">
         <v>5</v>
       </c>
-      <c r="F53" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G53" s="3">
+      <c r="G53" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" s="3">
         <v>4060005</v>
       </c>
-      <c r="H53" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="1:8">
+      <c r="I53" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:9">
       <c r="A54" s="4">
         <v>1802</v>
       </c>
@@ -2705,25 +2901,28 @@
         <v>9</v>
       </c>
       <c r="C54" s="4">
+        <v>101500001</v>
+      </c>
+      <c r="D54" s="4">
         <v>1109</v>
       </c>
-      <c r="D54" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E54" s="11">
+      <c r="E54" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F54" s="11">
         <v>15</v>
       </c>
-      <c r="F54" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" s="3">
         <v>4060005</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="1:8">
+      <c r="I54" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:9">
       <c r="A55" s="4">
         <v>1803</v>
       </c>
@@ -2731,25 +2930,28 @@
         <v>9</v>
       </c>
       <c r="C55" s="4">
+        <v>101500001</v>
+      </c>
+      <c r="D55" s="4">
         <v>1109</v>
       </c>
-      <c r="D55" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E55" s="11">
+      <c r="E55" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" s="11">
         <v>25</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="G55" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="I55" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G55" s="3">
-        <v>4060005</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="1:8">
+    </row>
+    <row r="56" customHeight="1" spans="1:9">
       <c r="A56" s="4">
         <v>1804</v>
       </c>
@@ -2757,25 +2959,28 @@
         <v>9</v>
       </c>
       <c r="C56" s="4">
+        <v>101500001</v>
+      </c>
+      <c r="D56" s="4">
         <v>1109</v>
       </c>
-      <c r="D56" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E56" s="11">
+      <c r="E56" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F56" s="11">
         <v>35</v>
       </c>
-      <c r="F56" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G56" s="3">
+      <c r="G56" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H56" s="3">
         <v>4060005</v>
       </c>
-      <c r="H56" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="1:8">
+      <c r="I56" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:9">
       <c r="A57" s="4">
         <v>1805</v>
       </c>
@@ -2783,25 +2988,28 @@
         <v>9</v>
       </c>
       <c r="C57" s="4">
+        <v>101500001</v>
+      </c>
+      <c r="D57" s="4">
         <v>1109</v>
       </c>
-      <c r="D57" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E57" s="11">
+      <c r="E57" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F57" s="11">
         <v>45</v>
       </c>
-      <c r="F57" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H57" s="3">
         <v>4060005</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="58" customHeight="1" spans="1:8">
+      <c r="I57" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:9">
       <c r="A58" s="4">
         <v>1806</v>
       </c>
@@ -2809,25 +3017,28 @@
         <v>9</v>
       </c>
       <c r="C58" s="4">
+        <v>101500001</v>
+      </c>
+      <c r="D58" s="4">
         <v>1109</v>
       </c>
-      <c r="D58" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="E58" s="11">
+      <c r="E58" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F58" s="11">
         <v>50</v>
       </c>
-      <c r="F58" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="G58" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H58" s="3">
         <v>4060005</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="59" customHeight="1" spans="1:8">
+      <c r="I58" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:9">
       <c r="A59" s="4">
         <v>1901</v>
       </c>
@@ -2835,25 +3046,28 @@
         <v>10</v>
       </c>
       <c r="C59" s="4">
+        <v>100700001</v>
+      </c>
+      <c r="D59" s="4">
         <v>1110</v>
       </c>
-      <c r="D59" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E59" s="11">
+      <c r="E59" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F59" s="11">
         <v>5</v>
       </c>
-      <c r="F59" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H59" s="3">
         <v>4060006</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" customHeight="1" spans="1:8">
+      <c r="I59" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:9">
       <c r="A60" s="4">
         <v>1902</v>
       </c>
@@ -2861,25 +3075,28 @@
         <v>10</v>
       </c>
       <c r="C60" s="4">
+        <v>100700001</v>
+      </c>
+      <c r="D60" s="4">
         <v>1110</v>
       </c>
-      <c r="D60" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E60" s="11">
+      <c r="E60" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F60" s="11">
         <v>15</v>
       </c>
-      <c r="F60" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H60" s="3">
         <v>4060006</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" customHeight="1" spans="1:8">
+      <c r="I60" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:9">
       <c r="A61" s="4">
         <v>1903</v>
       </c>
@@ -2887,25 +3104,28 @@
         <v>10</v>
       </c>
       <c r="C61" s="4">
+        <v>100700001</v>
+      </c>
+      <c r="D61" s="4">
         <v>1110</v>
       </c>
-      <c r="D61" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E61" s="11">
+      <c r="E61" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F61" s="11">
         <v>25</v>
       </c>
-      <c r="F61" s="11" t="s">
+      <c r="G61" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H61" s="3">
+        <v>4060006</v>
+      </c>
+      <c r="I61" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G61" s="3">
-        <v>4060006</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="1:8">
+    </row>
+    <row r="62" customHeight="1" spans="1:9">
       <c r="A62" s="4">
         <v>1904</v>
       </c>
@@ -2913,25 +3133,28 @@
         <v>10</v>
       </c>
       <c r="C62" s="4">
+        <v>100700001</v>
+      </c>
+      <c r="D62" s="4">
         <v>1110</v>
       </c>
-      <c r="D62" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E62" s="11">
+      <c r="E62" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F62" s="11">
         <v>35</v>
       </c>
-      <c r="F62" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="G62" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H62" s="3">
         <v>4060006</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="1:8">
+      <c r="I62" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="1:9">
       <c r="A63" s="4">
         <v>1905</v>
       </c>
@@ -2939,25 +3162,28 @@
         <v>10</v>
       </c>
       <c r="C63" s="4">
+        <v>100700001</v>
+      </c>
+      <c r="D63" s="4">
         <v>1110</v>
       </c>
-      <c r="D63" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E63" s="11">
+      <c r="E63" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F63" s="11">
         <v>45</v>
       </c>
-      <c r="F63" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G63" s="3">
+      <c r="G63" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H63" s="3">
         <v>4060006</v>
       </c>
-      <c r="H63" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="1:8">
+      <c r="I63" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="1:9">
       <c r="A64" s="4">
         <v>1906</v>
       </c>
@@ -2965,25 +3191,28 @@
         <v>10</v>
       </c>
       <c r="C64" s="4">
+        <v>100700001</v>
+      </c>
+      <c r="D64" s="4">
         <v>1110</v>
       </c>
-      <c r="D64" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E64" s="11">
+      <c r="E64" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F64" s="11">
         <v>50</v>
       </c>
-      <c r="F64" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G64" s="3">
+      <c r="G64" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="H64" s="3">
         <v>4060006</v>
       </c>
-      <c r="H64" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="1:8">
+      <c r="I64" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="1:9">
       <c r="A65" s="4">
         <v>2001</v>
       </c>
@@ -2991,25 +3220,28 @@
         <v>11</v>
       </c>
       <c r="C65" s="4">
+        <v>102200001</v>
+      </c>
+      <c r="D65" s="4">
         <v>1111</v>
       </c>
-      <c r="D65" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E65" s="11">
+      <c r="E65" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F65" s="11">
         <v>5</v>
       </c>
-      <c r="F65" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G65" s="3">
+      <c r="G65" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H65" s="3">
         <v>4060007</v>
       </c>
-      <c r="H65" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="1:8">
+      <c r="I65" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="1:9">
       <c r="A66" s="4">
         <v>2002</v>
       </c>
@@ -3017,25 +3249,28 @@
         <v>11</v>
       </c>
       <c r="C66" s="4">
+        <v>102200001</v>
+      </c>
+      <c r="D66" s="4">
         <v>1111</v>
       </c>
-      <c r="D66" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E66" s="11">
+      <c r="E66" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F66" s="11">
         <v>15</v>
       </c>
-      <c r="F66" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H66" s="3">
         <v>4060007</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="1:8">
+      <c r="I66" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="1:9">
       <c r="A67" s="4">
         <v>2003</v>
       </c>
@@ -3043,25 +3278,28 @@
         <v>11</v>
       </c>
       <c r="C67" s="4">
+        <v>102200001</v>
+      </c>
+      <c r="D67" s="4">
         <v>1111</v>
       </c>
-      <c r="D67" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E67" s="11">
+      <c r="E67" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F67" s="11">
         <v>25</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="G67" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H67" s="3">
+        <v>4060007</v>
+      </c>
+      <c r="I67" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G67" s="3">
-        <v>4060007</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="1:8">
+    </row>
+    <row r="68" customHeight="1" spans="1:9">
       <c r="A68" s="4">
         <v>2004</v>
       </c>
@@ -3069,25 +3307,28 @@
         <v>11</v>
       </c>
       <c r="C68" s="4">
+        <v>102200001</v>
+      </c>
+      <c r="D68" s="4">
         <v>1111</v>
       </c>
-      <c r="D68" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E68" s="11">
+      <c r="E68" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F68" s="11">
         <v>35</v>
       </c>
-      <c r="F68" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G68" s="3">
+      <c r="G68" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H68" s="3">
         <v>4060007</v>
       </c>
-      <c r="H68" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="1:8">
+      <c r="I68" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="1:9">
       <c r="A69" s="4">
         <v>2005</v>
       </c>
@@ -3095,25 +3336,28 @@
         <v>11</v>
       </c>
       <c r="C69" s="4">
+        <v>102200001</v>
+      </c>
+      <c r="D69" s="4">
         <v>1111</v>
       </c>
-      <c r="D69" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E69" s="11">
+      <c r="E69" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F69" s="11">
         <v>45</v>
       </c>
-      <c r="F69" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="G69" s="3">
+      <c r="G69" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H69" s="3">
         <v>4060007</v>
       </c>
-      <c r="H69" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="1:8">
+      <c r="I69" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="70" customHeight="1" spans="1:9">
       <c r="A70" s="4">
         <v>2006</v>
       </c>
@@ -3121,25 +3365,28 @@
         <v>11</v>
       </c>
       <c r="C70" s="4">
+        <v>102200001</v>
+      </c>
+      <c r="D70" s="4">
         <v>1111</v>
       </c>
-      <c r="D70" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="E70" s="11">
+      <c r="E70" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F70" s="11">
         <v>50</v>
       </c>
-      <c r="F70" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="G70" s="3">
+      <c r="G70" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H70" s="3">
         <v>4060007</v>
       </c>
-      <c r="H70" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="71" customHeight="1" spans="1:8">
+      <c r="I70" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="1:9">
       <c r="A71" s="4">
         <v>2101</v>
       </c>
@@ -3147,25 +3394,28 @@
         <v>12</v>
       </c>
       <c r="C71" s="4">
+        <v>102100001</v>
+      </c>
+      <c r="D71" s="4">
         <v>1112</v>
       </c>
-      <c r="D71" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E71" s="11">
+      <c r="E71" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F71" s="11">
         <v>5</v>
       </c>
-      <c r="F71" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G71" s="3">
+      <c r="G71" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H71" s="3">
         <v>4060008</v>
       </c>
-      <c r="H71" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="1:8">
+      <c r="I71" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="1:9">
       <c r="A72" s="4">
         <v>2102</v>
       </c>
@@ -3173,25 +3423,28 @@
         <v>12</v>
       </c>
       <c r="C72" s="4">
+        <v>102100001</v>
+      </c>
+      <c r="D72" s="4">
         <v>1112</v>
       </c>
-      <c r="D72" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E72" s="11">
+      <c r="E72" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F72" s="11">
         <v>15</v>
       </c>
-      <c r="F72" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H72" s="3">
         <v>4060008</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="1:8">
+      <c r="I72" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="1:9">
       <c r="A73" s="4">
         <v>2103</v>
       </c>
@@ -3199,25 +3452,28 @@
         <v>12</v>
       </c>
       <c r="C73" s="4">
+        <v>102100001</v>
+      </c>
+      <c r="D73" s="4">
         <v>1112</v>
       </c>
-      <c r="D73" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E73" s="11">
+      <c r="E73" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F73" s="11">
         <v>25</v>
       </c>
-      <c r="F73" s="11" t="s">
+      <c r="G73" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H73" s="3">
+        <v>4060008</v>
+      </c>
+      <c r="I73" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G73" s="3">
-        <v>4060008</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="1:8">
+    </row>
+    <row r="74" customHeight="1" spans="1:9">
       <c r="A74" s="4">
         <v>2104</v>
       </c>
@@ -3225,25 +3481,28 @@
         <v>12</v>
       </c>
       <c r="C74" s="4">
+        <v>102100001</v>
+      </c>
+      <c r="D74" s="4">
         <v>1112</v>
       </c>
-      <c r="D74" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E74" s="11">
+      <c r="E74" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F74" s="11">
         <v>35</v>
       </c>
-      <c r="F74" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G74" s="3">
+      <c r="G74" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H74" s="3">
         <v>4060008</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="1:8">
+      <c r="I74" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="1:9">
       <c r="A75" s="4">
         <v>2105</v>
       </c>
@@ -3251,25 +3510,28 @@
         <v>12</v>
       </c>
       <c r="C75" s="4">
+        <v>102100001</v>
+      </c>
+      <c r="D75" s="4">
         <v>1112</v>
       </c>
-      <c r="D75" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E75" s="11">
+      <c r="E75" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F75" s="11">
         <v>45</v>
       </c>
-      <c r="F75" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G75" s="3">
+      <c r="G75" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H75" s="3">
         <v>4060008</v>
       </c>
-      <c r="H75" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="1:8">
+      <c r="I75" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="1:9">
       <c r="A76" s="4">
         <v>2106</v>
       </c>
@@ -3277,25 +3539,171 @@
         <v>12</v>
       </c>
       <c r="C76" s="4">
+        <v>102100001</v>
+      </c>
+      <c r="D76" s="4">
         <v>1112</v>
       </c>
-      <c r="D76" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="E76" s="11">
+      <c r="E76" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="F76" s="11">
         <v>50</v>
       </c>
-      <c r="F76" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="G76" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H76" s="3">
         <v>4060008</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>43</v>
+      <c r="I76" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="1:9">
+      <c r="A77" s="4">
+        <v>2201</v>
+      </c>
+      <c r="B77" s="4">
+        <v>13</v>
+      </c>
+      <c r="C77" s="18">
+        <v>1150001</v>
+      </c>
+      <c r="E77" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F77" s="4">
+        <v>3</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H77" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="1:9">
+      <c r="A78" s="4">
+        <v>2202</v>
+      </c>
+      <c r="B78" s="4">
+        <v>13</v>
+      </c>
+      <c r="C78" s="18">
+        <v>1150001</v>
+      </c>
+      <c r="E78" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="F78" s="4">
+        <v>6</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="1:9">
+      <c r="A79" s="4">
+        <v>2301</v>
+      </c>
+      <c r="B79" s="4">
+        <v>14</v>
+      </c>
+      <c r="C79" s="18">
+        <v>1150002</v>
+      </c>
+      <c r="E79" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="1:9">
+      <c r="A80" s="4">
+        <v>2401</v>
+      </c>
+      <c r="B80" s="4">
+        <v>15</v>
+      </c>
+      <c r="C80" s="18">
+        <v>1150008</v>
+      </c>
+      <c r="E80" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:5">
+      <c r="A81" s="4">
+        <v>2501</v>
+      </c>
+      <c r="B81" s="4">
+        <v>16</v>
+      </c>
+      <c r="C81" s="18">
+        <v>1150035</v>
+      </c>
+      <c r="E81" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:5">
+      <c r="A82" s="4">
+        <v>2601</v>
+      </c>
+      <c r="B82" s="4">
+        <v>17</v>
+      </c>
+      <c r="C82" s="18">
+        <v>1150013</v>
+      </c>
+      <c r="E82" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:5">
+      <c r="A83" s="4">
+        <v>2701</v>
+      </c>
+      <c r="B83" s="4">
+        <v>18</v>
+      </c>
+      <c r="C83" s="18">
+        <v>1150032</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="C77">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C78">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C79">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C80">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C81">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C82">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C83">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/hall/resources/sample/MedalBuff.xlsx
+++ b/hall/resources/sample/MedalBuff.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="66">
   <si>
     <t>序号</t>
   </si>
@@ -3625,6 +3625,18 @@
       <c r="E79" s="11" t="s">
         <v>61</v>
       </c>
+      <c r="F79" s="4">
+        <v>3</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H79" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="80" customHeight="1" spans="1:9">
       <c r="A80" s="4">
@@ -3639,8 +3651,20 @@
       <c r="E80" s="11" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="81" customHeight="1" spans="1:5">
+      <c r="F80" s="4">
+        <v>3</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H80" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="1:9">
       <c r="A81" s="4">
         <v>2501</v>
       </c>
@@ -3653,8 +3677,20 @@
       <c r="E81" s="11" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="82" customHeight="1" spans="1:5">
+      <c r="F81" s="4">
+        <v>3</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H81" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="1:9">
       <c r="A82" s="4">
         <v>2601</v>
       </c>
@@ -3667,8 +3703,20 @@
       <c r="E82" s="11" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="83" customHeight="1" spans="1:5">
+      <c r="F82" s="4">
+        <v>3</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H82" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:9">
       <c r="A83" s="4">
         <v>2701</v>
       </c>
@@ -3680,6 +3728,18 @@
       </c>
       <c r="E83" s="11" t="s">
         <v>65</v>
+      </c>
+      <c r="F83" s="4">
+        <v>3</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H83" s="3">
+        <v>4060005</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/MedalBuff.xlsx
+++ b/hall/resources/sample/MedalBuff.xlsx
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="59">
   <si>
     <t>序号</t>
   </si>
@@ -197,27 +197,6 @@
   </si>
   <si>
     <t>财神来了</t>
-  </si>
-  <si>
-    <t>13_100</t>
-  </si>
-  <si>
-    <t>[观看广告]金币收益：+(%s)</t>
-  </si>
-  <si>
-    <t>13_150</t>
-  </si>
-  <si>
-    <t>13_200</t>
-  </si>
-  <si>
-    <t>13_250</t>
-  </si>
-  <si>
-    <t>13_300</t>
-  </si>
-  <si>
-    <t>13_350</t>
   </si>
   <si>
     <t>寒冰王座</t>
@@ -476,12 +455,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2010,13 +1989,13 @@
         <v>5</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="H23" s="3">
-        <v>4060008</v>
+        <v>4060005</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" s="3" customFormat="1" customHeight="1" spans="1:13">
@@ -2039,13 +2018,13 @@
         <v>15</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="H24" s="3">
-        <v>4060008</v>
+        <v>4060005</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="M24" s="12"/>
     </row>
@@ -2069,13 +2048,13 @@
         <v>25</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="H25" s="3">
-        <v>4060008</v>
+        <v>4060005</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="M25" s="12"/>
     </row>
@@ -2099,13 +2078,13 @@
         <v>35</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H26" s="3">
-        <v>4060008</v>
+        <v>4060005</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" s="3" customFormat="1" customHeight="1" spans="1:13">
@@ -2128,13 +2107,13 @@
         <v>45</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H27" s="3">
-        <v>4060008</v>
+        <v>4060005</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="M27" s="12"/>
     </row>
@@ -2158,13 +2137,13 @@
         <v>50</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="H28" s="3">
-        <v>4060008</v>
+        <v>4060005</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="M28" s="12"/>
     </row>
@@ -2182,19 +2161,19 @@
         <v>1105</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F29" s="11">
         <v>5</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H29" s="3">
-        <v>4060005</v>
+        <v>4060006</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:13">
@@ -2211,19 +2190,19 @@
         <v>1105</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F30" s="11">
         <v>15</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H30" s="3">
-        <v>4060005</v>
+        <v>4060006</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" customHeight="1" spans="1:13">
@@ -2240,19 +2219,19 @@
         <v>1105</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F31" s="11">
         <v>25</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H31" s="3">
-        <v>4060005</v>
+        <v>4060006</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="1:13">
@@ -2269,19 +2248,19 @@
         <v>1105</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F32" s="11">
         <v>35</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H32" s="3">
-        <v>4060005</v>
+        <v>4060006</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="1:9">
@@ -2298,19 +2277,19 @@
         <v>1105</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F33" s="11">
         <v>45</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H33" s="3">
-        <v>4060005</v>
+        <v>4060006</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" customHeight="1" spans="1:9">
@@ -2327,19 +2306,19 @@
         <v>1105</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F34" s="11">
         <v>50</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="H34" s="3">
-        <v>4060005</v>
+        <v>4060006</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" customHeight="1" spans="1:9">
@@ -2356,19 +2335,19 @@
         <v>1106</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F35" s="11">
         <v>5</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H35" s="3">
-        <v>4060006</v>
+        <v>4060007</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" customHeight="1" spans="1:9">
@@ -2385,19 +2364,19 @@
         <v>1106</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F36" s="11">
         <v>15</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="H36" s="3">
-        <v>4060006</v>
+        <v>4060007</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" customHeight="1" spans="1:9">
@@ -2414,19 +2393,19 @@
         <v>1106</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F37" s="11">
         <v>25</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H37" s="3">
-        <v>4060006</v>
+        <v>4060007</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:9">
@@ -2443,19 +2422,19 @@
         <v>1106</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F38" s="11">
         <v>35</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H38" s="3">
-        <v>4060006</v>
+        <v>4060007</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" customHeight="1" spans="1:9">
@@ -2472,19 +2451,19 @@
         <v>1106</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F39" s="11">
         <v>45</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H39" s="3">
-        <v>4060006</v>
+        <v>4060007</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="1:9">
@@ -2501,19 +2480,19 @@
         <v>1106</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F40" s="11">
         <v>50</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H40" s="3">
-        <v>4060006</v>
+        <v>4060007</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41" customHeight="1" spans="1:9">
@@ -2530,19 +2509,19 @@
         <v>1107</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F41" s="11">
         <v>5</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="H41" s="3">
-        <v>4060007</v>
+        <v>4060005</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="1:9">
@@ -2559,19 +2538,19 @@
         <v>1107</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F42" s="11">
         <v>15</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="H42" s="3">
-        <v>4060007</v>
+        <v>4060005</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="1:9">
@@ -2588,19 +2567,19 @@
         <v>1107</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F43" s="11">
         <v>25</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="H43" s="3">
-        <v>4060007</v>
+        <v>4060005</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" customHeight="1" spans="1:9">
@@ -2617,19 +2596,19 @@
         <v>1107</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F44" s="11">
         <v>35</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="H44" s="3">
-        <v>4060007</v>
+        <v>4060005</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" customHeight="1" spans="1:9">
@@ -2646,19 +2625,19 @@
         <v>1107</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F45" s="11">
         <v>45</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="H45" s="3">
-        <v>4060007</v>
+        <v>4060005</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:9">
@@ -2675,19 +2654,19 @@
         <v>1107</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F46" s="11">
         <v>50</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="H46" s="3">
-        <v>4060007</v>
+        <v>4060005</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:9">
@@ -2704,19 +2683,19 @@
         <v>1108</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F47" s="11">
         <v>5</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="H47" s="3">
-        <v>4060008</v>
+        <v>4060006</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" customHeight="1" spans="1:9">
@@ -2733,19 +2712,19 @@
         <v>1108</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F48" s="11">
         <v>15</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H48" s="3">
-        <v>4060008</v>
+        <v>4060006</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:9">
@@ -2762,19 +2741,19 @@
         <v>1108</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F49" s="11">
         <v>25</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="H49" s="3">
-        <v>4060008</v>
+        <v>4060006</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:9">
@@ -2791,19 +2770,19 @@
         <v>1108</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F50" s="11">
         <v>35</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="H50" s="3">
-        <v>4060008</v>
+        <v>4060006</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:9">
@@ -2820,19 +2799,19 @@
         <v>1108</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F51" s="11">
         <v>45</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="H51" s="3">
-        <v>4060008</v>
+        <v>4060006</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:9">
@@ -2849,19 +2828,19 @@
         <v>1108</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="F52" s="11">
         <v>50</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="H52" s="3">
-        <v>4060008</v>
+        <v>4060006</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:9">
@@ -2878,19 +2857,19 @@
         <v>1109</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F53" s="11">
         <v>5</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="H53" s="3">
-        <v>4060005</v>
+        <v>4060007</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="1:9">
@@ -2907,19 +2886,19 @@
         <v>1109</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F54" s="11">
         <v>15</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="H54" s="3">
-        <v>4060005</v>
+        <v>4060007</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55" customHeight="1" spans="1:9">
@@ -2936,19 +2915,19 @@
         <v>1109</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F55" s="11">
         <v>25</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H55" s="3">
-        <v>4060005</v>
+        <v>4060007</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" customHeight="1" spans="1:9">
@@ -2965,19 +2944,19 @@
         <v>1109</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F56" s="11">
         <v>35</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="H56" s="3">
-        <v>4060005</v>
+        <v>4060007</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="57" customHeight="1" spans="1:9">
@@ -2994,19 +2973,19 @@
         <v>1109</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F57" s="11">
         <v>45</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="H57" s="3">
-        <v>4060005</v>
+        <v>4060007</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="1:9">
@@ -3023,19 +3002,19 @@
         <v>1109</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F58" s="11">
         <v>50</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="H58" s="3">
-        <v>4060005</v>
+        <v>4060007</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" customHeight="1" spans="1:9">
@@ -3052,19 +3031,19 @@
         <v>1110</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F59" s="11">
         <v>5</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H59" s="3">
-        <v>4060006</v>
+        <v>4060005</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:9">
@@ -3081,19 +3060,19 @@
         <v>1110</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F60" s="11">
         <v>15</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H60" s="3">
-        <v>4060006</v>
+        <v>4060005</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" customHeight="1" spans="1:9">
@@ -3110,19 +3089,19 @@
         <v>1110</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F61" s="11">
         <v>25</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="H61" s="3">
-        <v>4060006</v>
+        <v>4060005</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:9">
@@ -3139,19 +3118,19 @@
         <v>1110</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F62" s="11">
         <v>35</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="H62" s="3">
-        <v>4060006</v>
+        <v>4060005</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" customHeight="1" spans="1:9">
@@ -3168,19 +3147,19 @@
         <v>1110</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F63" s="11">
         <v>45</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H63" s="3">
-        <v>4060006</v>
+        <v>4060005</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" customHeight="1" spans="1:9">
@@ -3197,19 +3176,19 @@
         <v>1110</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F64" s="11">
         <v>50</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H64" s="3">
-        <v>4060006</v>
+        <v>4060005</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" customHeight="1" spans="1:9">
@@ -3226,19 +3205,19 @@
         <v>1111</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F65" s="11">
         <v>5</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="H65" s="3">
-        <v>4060007</v>
+        <v>4060006</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="66" customHeight="1" spans="1:9">
@@ -3255,19 +3234,19 @@
         <v>1111</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F66" s="11">
         <v>15</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H66" s="3">
-        <v>4060007</v>
+        <v>4060006</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" customHeight="1" spans="1:9">
@@ -3284,19 +3263,19 @@
         <v>1111</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F67" s="11">
         <v>25</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H67" s="3">
-        <v>4060007</v>
+        <v>4060006</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" customHeight="1" spans="1:9">
@@ -3313,19 +3292,19 @@
         <v>1111</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F68" s="11">
         <v>35</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="H68" s="3">
-        <v>4060007</v>
+        <v>4060006</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69" customHeight="1" spans="1:9">
@@ -3342,19 +3321,19 @@
         <v>1111</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F69" s="11">
         <v>45</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H69" s="3">
-        <v>4060007</v>
+        <v>4060006</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="70" customHeight="1" spans="1:9">
@@ -3371,19 +3350,19 @@
         <v>1111</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F70" s="11">
         <v>50</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H70" s="3">
-        <v>4060007</v>
+        <v>4060006</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="1:9">
@@ -3400,19 +3379,19 @@
         <v>1112</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F71" s="11">
         <v>5</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H71" s="3">
-        <v>4060008</v>
+        <v>4060007</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="1:9">
@@ -3429,19 +3408,19 @@
         <v>1112</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F72" s="11">
         <v>15</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H72" s="3">
-        <v>4060008</v>
+        <v>4060007</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="73" customHeight="1" spans="1:9">
@@ -3458,19 +3437,19 @@
         <v>1112</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F73" s="11">
         <v>25</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="H73" s="3">
-        <v>4060008</v>
+        <v>4060007</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="1:9">
@@ -3487,19 +3466,19 @@
         <v>1112</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F74" s="11">
         <v>35</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H74" s="3">
-        <v>4060008</v>
+        <v>4060007</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="1:9">
@@ -3516,19 +3495,19 @@
         <v>1112</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F75" s="11">
         <v>45</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H75" s="3">
-        <v>4060008</v>
+        <v>4060007</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76" customHeight="1" spans="1:9">
@@ -3545,19 +3524,19 @@
         <v>1112</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F76" s="11">
         <v>50</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H76" s="3">
-        <v>4060008</v>
+        <v>4060007</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="1:9">
@@ -3571,13 +3550,13 @@
         <v>1150001</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F77" s="4">
         <v>3</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H77" s="3">
         <v>4060005</v>
@@ -3597,7 +3576,7 @@
         <v>1150001</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F78" s="4">
         <v>6</v>
@@ -3623,13 +3602,13 @@
         <v>1150002</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F79" s="4">
         <v>3</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H79" s="3">
         <v>4060005</v>
@@ -3649,13 +3628,13 @@
         <v>1150008</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F80" s="4">
         <v>3</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H80" s="3">
         <v>4060005</v>
@@ -3675,13 +3654,13 @@
         <v>1150035</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F81" s="4">
         <v>3</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H81" s="3">
         <v>4060005</v>
@@ -3701,13 +3680,13 @@
         <v>1150013</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F82" s="4">
         <v>3</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H82" s="3">
         <v>4060005</v>
@@ -3727,13 +3706,13 @@
         <v>1150032</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F83" s="4">
         <v>3</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H83" s="3">
         <v>4060005</v>
